--- a/output/full_scan/batch_seq6_2026-10-22.xlsx
+++ b/output/full_scan/batch_seq6_2026-10-22.xlsx
@@ -440,11 +440,11 @@
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>942.5179190923382</v>
+        <v>1132.517919092338</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>201</v>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>78.90131159300442</v>
+        <v>78.90131148220883</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>33.15849059217958</v>
+        <v>33.15849057183254</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.887832827195892</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -574,27 +574,27 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6245</v>
+        <v>6277</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>777.237312605263</v>
+        <v>915.8527193049849</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>90.09999999999999</v>
+        <v>100.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>60.41895126737322</v>
+        <v>88.80743659518778</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>33.02733245355147</v>
+        <v>40.42124230723691</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.281559472437752</v>
+        <v>4.685271930498494</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.0274152687069215</v>
+        <v>2.338155083939738</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6277</v>
+        <v>6246</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>775.8527193049849</v>
+        <v>869.3926353690457</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>100.5</v>
+        <v>13.4</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>88.80743662143306</v>
+        <v>67.03613213401631</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>40.42124229421223</v>
+        <v>19.45238165251561</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>4.685271930498494</v>
+        <v>2.026592574560778</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>2.338155083963786</v>
+        <v>0.04737782222289627</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, breakout_20d, hist_turn_positive, stronger_than_market, bb_squeeze_breakout, breakout_volume_confirm, williams_r_recovery, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6246</v>
+        <v>6456</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>759.3926353690457</v>
+        <v>860.7365689750428</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13.4</v>
+        <v>102</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>67.03613243886718</v>
+        <v>65.64072220204432</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>19.45238176324445</v>
+        <v>34.890155062347</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.026592574560778</v>
+        <v>2.416036974209795</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.047377822174828</v>
+        <v>-0.3201726229756376</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, bb_squeeze_breakout, breakout_volume_confirm, williams_r_recovery, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6456</v>
+        <v>6173</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>720.7365689750428</v>
+        <v>860.6949523388494</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>102</v>
+        <v>293.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,49 +764,49 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>65.64072223582033</v>
+        <v>55.08568304782916</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>34.89015496442743</v>
+        <v>36.65148666452099</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.416036974209795</v>
+        <v>1.233027650764054</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.3201726237207145</v>
+        <v>-5.186169113455673</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6173</v>
+        <v>6245</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>665.6949523388494</v>
+        <v>857.237312605263</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>293.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>55.08568305714872</v>
+        <v>60.41895108188609</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>36.65148649029069</v>
+        <v>33.02733244354248</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.233027650764054</v>
+        <v>1.281559472437751</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-5.186169113435064</v>
+        <v>0.02741526892322721</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6213</v>
+        <v>6416</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>644.5433356822714</v>
+        <v>792.7360712998213</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>777</v>
+        <v>119.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>60.52530555462479</v>
+        <v>54.64295262449493</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>31.63464735423176</v>
+        <v>33.47085422785257</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.53425075941183</v>
+        <v>0.6145525805647692</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-5.09921683890073</v>
+        <v>-0.6052151002842892</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6209</v>
+        <v>6234</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>640.1159343719399</v>
+        <v>771.9961132399337</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>99</v>
+        <v>49.05</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>60.06618490150322</v>
+        <v>66.14815018164282</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>49.94953710808068</v>
+        <v>33.13629603199323</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.398229788631511</v>
+        <v>2.544511166061138</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.547504951277292</v>
+        <v>0.7480122025300724</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6416</v>
+        <v>6209</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>637.7360712998213</v>
+        <v>750.1159343719399</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>119.5</v>
+        <v>99</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>54.6429527020617</v>
+        <v>60.06618486530025</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>33.47085420366837</v>
+        <v>49.94953713038884</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.6145525805647692</v>
+        <v>1.398229788631511</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.6052151006928885</v>
+        <v>1.547504951229226</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6234</v>
+        <v>6269</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>631.9961132399339</v>
+        <v>747.6604412963084</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>49.05</v>
+        <v>78.7</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>66.14815020744646</v>
+        <v>59.64192345871853</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>33.13629601896487</v>
+        <v>26.41004630783667</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.544511166061138</v>
+        <v>3.166044129630837</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.7480122027463834</v>
+        <v>2.003902512995683</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6438</v>
+        <v>6233</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>629.0851608813601</v>
+        <v>712.1949567710934</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>164</v>
+        <v>26.85</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>49.94045142284076</v>
+        <v>82.00485215658971</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>36.37853721587477</v>
+        <v>52.30388539492535</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.6998040680600051</v>
+        <v>2.033008627467827</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.9585343489723144</v>
+        <v>0.2300014572477103</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6278</v>
+        <v>6438</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>617.0756017908365</v>
+        <v>689.0851608813601</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>290.5</v>
+        <v>164</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>64.81172468423836</v>
+        <v>49.94045097420253</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>51.30590224175009</v>
+        <v>36.37853756754624</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.252859594182261</v>
+        <v>0.6998040680600051</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>3.795119548270153</v>
+        <v>-0.9585343456074904</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6233</v>
+        <v>6470</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>602.1949567710936</v>
+        <v>677.0219967973202</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>26.85</v>
+        <v>45.9</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>82.00485244344623</v>
+        <v>68.14931605877572</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>52.30388538148929</v>
+        <v>35.44148197183497</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2.033008627467827</v>
+        <v>0.6476559223050367</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.2300014572597242</v>
+        <v>0.2317171874937166</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6470</v>
+        <v>6194</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>597.0219967973214</v>
+        <v>673.8203676915855</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>45.9</v>
+        <v>32.6</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>68.14931619018421</v>
+        <v>69.44974521961467</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>35.44148200778917</v>
+        <v>41.35617004318013</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.6476559223050367</v>
+        <v>5.971524141804417</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.2317171874696848</v>
+        <v>0.07751029843398038</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, avoid_chase, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6194</v>
+        <v>6278</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>591.4573796922498</v>
+        <v>672.0756017908365</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>32.6</v>
+        <v>290.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,49 +1294,49 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>69.44974563747616</v>
+        <v>64.81172466953879</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>41.35616934745384</v>
+        <v>51.30590219839804</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.8807821029947862</v>
+        <v>1.252859594182261</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.0775102978811833</v>
+        <v>3.795119548270154</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6226</v>
+        <v>6191</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>光鼎</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>573.5581897158627</v>
+        <v>640.8772581040774</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>37.75</v>
+        <v>89.8</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>43.96007259421872</v>
+        <v>53.90440080384538</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>36.05988866262124</v>
+        <v>28.80512445100012</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.5113305909110898</v>
+        <v>0.6183082921517314</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-1.205038108061476</v>
+        <v>0.102891322796602</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6269</v>
+        <v>6168</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>562.6604412963084</v>
+        <v>632.3613167618937</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>78.7</v>
+        <v>34.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,49 +1400,49 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>59.64192349730473</v>
+        <v>42.48192274653715</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>26.41004622862789</v>
+        <v>30.04794274966148</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>3.166044129630837</v>
+        <v>0.2501599396096814</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>2.003902512995684</v>
+        <v>-1.291802676947541</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6204</v>
+        <v>6415</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>553.2204727641994</v>
+        <v>619.4782183600228</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>104.5</v>
+        <v>472</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>50.04581618235199</v>
+        <v>55.82687224204486</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>24.01983918753201</v>
+        <v>22.08385971397313</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.4830325583215399</v>
+        <v>1.865041219778342</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-1.378983245312027</v>
+        <v>4.10893205517692</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6225</v>
+        <v>6170</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>548.3699263967025</v>
+        <v>610.6013962923112</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>56.53966587385108</v>
+        <v>61.7646697223823</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>31.24587084345289</v>
+        <v>25.2116578831926</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.340775920971559</v>
+        <v>1.140741378769861</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.125044983972316</v>
+        <v>0.07249027042325401</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6271</v>
+        <v>6207</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>544.4353230354108</v>
+        <v>600.7210305817621</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>215</v>
+        <v>131.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>41.01842366791718</v>
+        <v>50.40165483345383</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>22.25653632709139</v>
+        <v>26.14804709642917</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.7881131899594851</v>
+        <v>0.5791253972083167</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-3.01694912809316</v>
+        <v>-1.693799943306909</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6415</v>
+        <v>6196</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>539.4672635108558</v>
+        <v>577.4650523533123</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>472</v>
+        <v>597</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>55.82687227032734</v>
+        <v>50.72621450008403</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>22.0838596196218</v>
+        <v>31.53902368895329</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.85613647689659</v>
+        <v>0.4832205599883757</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>4.108932057219778</v>
+        <v>-8.311415719534434</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6292</v>
+        <v>6198</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>534.0332133947204</v>
+        <v>571.9514534984928</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>65</v>
+        <v>19.55</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>45.64879489962596</v>
+        <v>52.29308520893061</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>26.36145672604278</v>
+        <v>7.38586692747694</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.6606877362996376</v>
+        <v>0.9435408730111927</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.5764223441812569</v>
+        <v>0.3680997728875546</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6170</v>
+        <v>6257</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>530.6013962923112</v>
+        <v>571.7477354972317</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>50</v>
+        <v>232</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,49 +1718,49 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>61.76466979656143</v>
+        <v>42.43749228234979</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>25.21165765849484</v>
+        <v>28.93118720321106</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.140741378769861</v>
+        <v>0.5603887573874565</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.0724902705914993</v>
+        <v>-5.813970493924819</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6218</v>
+        <v>6213</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>526.4561410542821</v>
+        <v>569.5433356822714</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>50.4</v>
+        <v>777</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,49 +1771,49 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>44.38903008785086</v>
+        <v>60.52530551074071</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>24.47871259900018</v>
+        <v>31.63464733604794</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4188212073909783</v>
+        <v>2.53425075941183</v>
       </c>
       <c r="K25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-1.497159607408192</v>
+        <v>-5.099216836016609</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6196</v>
+        <v>6418</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>522.4650523533123</v>
+        <v>561</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>597</v>
+        <v>43.65</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>50.72621448332954</v>
+        <v>66.95384630257544</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>31.53902363817422</v>
+        <v>36.24106969199593</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4832205599883756</v>
+        <v>13.57004154429711</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-8.311415719534434</v>
+        <v>1.280897501275817</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6207</v>
+        <v>6192</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>520.7210305817621</v>
+        <v>558.1509004929644</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>131.5</v>
+        <v>115</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>50.40165488488778</v>
+        <v>58.25200564476405</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>26.14804705603175</v>
+        <v>23.8649010645223</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5791253972083167</v>
+        <v>1.29480849990638</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-1.693799943114626</v>
+        <v>0.46874137484461</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>rsi_strong, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6257</v>
+        <v>6465</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>516.7477354972317</v>
+        <v>548.2128851983215</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>232</v>
+        <v>41.85</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>42.43749231524745</v>
+        <v>43.48960106896989</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>28.9311873382943</v>
+        <v>21.20336229737828</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.5603887573874565</v>
+        <v>2.152664272709147</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-5.813970494501639</v>
+        <v>0.4155686625625881</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6263</v>
+        <v>6226</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>514.7671153261587</v>
+        <v>533.5581897158627</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>169</v>
+        <v>37.75</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>51.9979942079497</v>
+        <v>43.96007259048138</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>28.03045121744395</v>
+        <v>36.05988863148296</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.8073056122401421</v>
+        <v>0.5113305909110898</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.3724378735838334</v>
+        <v>-1.20503810805427</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6197</v>
+        <v>6426</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>511.6897327308895</v>
+        <v>516.5468800395696</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,49 +2036,49 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>43.03512731325473</v>
+        <v>45.18736472900692</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>22.96535418188248</v>
+        <v>22.21152687383203</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.743549978550329</v>
+        <v>0.7864727676954077</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-5.5264737313612</v>
+        <v>-6.192578774217576</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6291</v>
+        <v>6205</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>504.4916265788801</v>
+        <v>513.9782578914923</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>363</v>
+        <v>65</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>30.97607552729326</v>
+        <v>43.41363655403386</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>29.10603310972443</v>
+        <v>20.82924988418803</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.4070879222902932</v>
+        <v>0.1866793272497344</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-11.86443332187347</v>
+        <v>-0.7767470553439226</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6465</v>
+        <v>6204</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>493.2128851983215</v>
+        <v>493.2204727641994</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>41.85</v>
+        <v>104.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>43.48960114295655</v>
+        <v>50.04581624807792</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>21.20336229737828</v>
+        <v>24.01983924377861</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>2.152664272709147</v>
+        <v>0.4830325583215399</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.4155686624596099</v>
+        <v>-1.378983245600434</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6198</v>
+        <v>6225</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>491.951453498493</v>
+        <v>488.3699263967025</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>19.55</v>
+        <v>77</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>52.29308520340023</v>
+        <v>56.53966589481185</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>7.38586690587972</v>
+        <v>31.24587084498942</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.9435408730111928</v>
+        <v>0.3407759209715591</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.3680997730077274</v>
+        <v>0.1250449838521526</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6192</v>
+        <v>6201</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>478.1509004929645</v>
+        <v>487.2097275784325</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>115</v>
+        <v>46</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>58.25200597356641</v>
+        <v>57.32572715890439</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>23.86490095581731</v>
+        <v>40.65618556437843</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.29480849990638</v>
+        <v>0.8579285059578369</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.4687413746042702</v>
+        <v>0.1599100456371082</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6227</v>
+        <v>6446</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>474.9652458087712</v>
+        <v>476.7962478590345</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>120.5</v>
+        <v>1160</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,49 +2301,49 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>40.20477844136433</v>
+        <v>43.43573046159274</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>25.5224655105318</v>
+        <v>10.92814114056611</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.4165843898479346</v>
+        <v>0.6308991060770219</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-2.115153760662388</v>
+        <v>3.220756256699413</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6449</v>
+        <v>6271</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>471.3314252080012</v>
+        <v>474.4353230354108</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,49 +2354,49 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>43.6231683177145</v>
+        <v>41.01842364847722</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>21.68590000065718</v>
+        <v>22.25653640119004</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.5971790049014803</v>
+        <v>0.7881131899594851</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-1.9823130151294</v>
+        <v>-3.016949127973012</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6191</v>
+        <v>6292</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>470.8772581040769</v>
+        <v>474.0332133947205</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>89.8</v>
+        <v>65</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>53.9044017848441</v>
+        <v>45.64879485948919</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>28.80512387051321</v>
+        <v>26.36145669580239</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.6183082921517314</v>
+        <v>0.6606877362996376</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.1028913196721004</v>
+        <v>-0.5764223441692444</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6168</v>
+        <v>6218</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>462.3613167618938</v>
+        <v>466.456141054282</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>34.5</v>
+        <v>50.4</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>42.48192273829374</v>
+        <v>44.38903008910564</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>30.04794303624139</v>
+        <v>24.47871259229134</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.2501599396096814</v>
+        <v>0.4188212073909783</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-1.291802677404204</v>
+        <v>-1.497159607456259</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6426</v>
+        <v>6263</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>461.5468800395696</v>
+        <v>454.7671153261587</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>313</v>
+        <v>169</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>45.1873647524362</v>
+        <v>51.99799419613434</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>22.21152695323068</v>
+        <v>28.03045116843188</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.7864727676954077</v>
+        <v>0.8073056122401421</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-6.192578774385797</v>
+        <v>-0.3724378738241652</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6205</v>
+        <v>6197</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>458.9782578914922</v>
+        <v>451.6897327308894</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>65</v>
+        <v>317</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>43.41363662703717</v>
+        <v>43.03512729454533</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>20.82924990858642</v>
+        <v>22.96535417764487</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.1866793272497343</v>
+        <v>0.743549978550329</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.7767470556082905</v>
+        <v>-5.526473731241047</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6175</v>
+        <v>6210</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>450.3716792665689</v>
+        <v>448.7890260317169</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>66.40000000000001</v>
+        <v>18.85</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>36.51630037612151</v>
+        <v>54.17252468642187</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>17.05801344530982</v>
+        <v>6.465255335144739</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.6658116057695529</v>
+        <v>0.4978017104403912</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.748569672765848</v>
+        <v>-0.003570395288495787</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6190</v>
+        <v>6291</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>447.7442054053462</v>
+        <v>444.4916265788801</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>64.7</v>
+        <v>363</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>35.69826604207853</v>
+        <v>30.97607550061628</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>22.20425640834058</v>
+        <v>29.10603318326356</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.6613033381130128</v>
+        <v>0.4070879222902932</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-1.095400227577466</v>
+        <v>-11.86443332235417</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6285</v>
+        <v>6409</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>432.9329532052843</v>
+        <v>443.2818300350433</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>230</v>
+        <v>910</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>42.46093502630335</v>
+        <v>51.47606461986035</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>22.68086876249616</v>
+        <v>15.70882893857922</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.209624947391127</v>
+        <v>0.7153998161566312</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-1.472203857415822</v>
+        <v>6.120000213229346</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, stronger_than_market, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6201</v>
+        <v>6224</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>432.2097275784325</v>
+        <v>432.5453307429132</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>46</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>57.32572707185376</v>
+        <v>43.07001023667062</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>40.65618556028402</v>
+        <v>20.31186054987297</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.8579285059578369</v>
+        <v>0.7271413870251814</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.1599100458293833</v>
+        <v>-0.6595038249322008</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6174</v>
+        <v>6462</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>422.1305553446718</v>
+        <v>425.7006018832118</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>49.3</v>
+        <v>96.3</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>46.96597950310033</v>
+        <v>43.07267987866539</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>17.75779139314793</v>
+        <v>16.10236338725004</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.504251063292833</v>
+        <v>0.8213115440132339</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.9111276447059732</v>
+        <v>-0.6177699439458755</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6446</v>
+        <v>6166</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>421.7962478590345</v>
+        <v>425.3396473012075</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1160</v>
+        <v>103.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,49 +2884,49 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>43.43573045500597</v>
+        <v>29.0488010639813</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>10.92814108787192</v>
+        <v>24.00473785967107</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.6308991060770219</v>
+        <v>0.4395881901848726</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M46" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>3.22075625802136</v>
+        <v>-2.287462812053302</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6418</v>
+        <v>6244</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>421</v>
+        <v>422.409709494459</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>43.65</v>
+        <v>21.2</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>66.9538462778805</v>
+        <v>39.33646446054198</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>36.2410696908726</v>
+        <v>15.1739034166078</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>13.57004154429711</v>
+        <v>0.7280176980431818</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>1.280897501311866</v>
+        <v>-0.1138734202031115</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6187</v>
+        <v>6164</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>419.8751078865902</v>
+        <v>419.5225993511321</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>1260</v>
+        <v>12.4</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>41.98032749467293</v>
+        <v>48.26300861798374</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>23.61668684935605</v>
+        <v>31.6518677951872</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6541503900630486</v>
+        <v>1.577254236615266</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-28.88229394257302</v>
+        <v>-0.05353483125443645</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6163</v>
+        <v>6227</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>華電網</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>418.10734752437</v>
+        <v>414.9652458087712</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>40.5</v>
+        <v>120.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>42.34963727054181</v>
+        <v>40.20477865001131</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>20.04113874424316</v>
+        <v>25.52246550091668</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.7065556234253727</v>
+        <v>0.4165843898479347</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.333304315278828</v>
+        <v>-2.115153760662388</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6467</v>
+        <v>6449</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>泰合</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>417.7256129865802</v>
+        <v>411.3314252080012</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>202.5</v>
+        <v>222</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>45.09504445526672</v>
+        <v>43.6231682260992</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>23.82667911020349</v>
+        <v>21.6859000493734</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.176351588861237</v>
+        <v>0.5971790049014803</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-6.293124573586726</v>
+        <v>-1.982313014288239</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6451</v>
+        <v>6175</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>396.9260365936099</v>
+        <v>390.3716792665684</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>351</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>36.48514493952683</v>
+        <v>36.51630034547541</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>20.51815877269546</v>
+        <v>17.05801338360466</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.7673668027537495</v>
+        <v>0.6658116057695529</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-4.996363063603033</v>
+        <v>-0.7485696728379544</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6282</v>
+        <v>6190</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>388.4834126162049</v>
+        <v>387.7442054053454</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>41.7</v>
+        <v>64.7</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>42.3068881585344</v>
+        <v>35.69826603924925</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>15.29926201259498</v>
+        <v>22.2042564816358</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.6291091592888773</v>
+        <v>0.6613033381130128</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.1351173204152688</v>
+        <v>-1.095400227601492</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6265</v>
+        <v>6165</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>384.4280184735205</v>
+        <v>380.1841637473945</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>43.9</v>
+        <v>48.65</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>32.03038263079091</v>
+        <v>49.63021911942405</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>24.49085406097723</v>
+        <v>13.52333650413539</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.58591246754207</v>
+        <v>0.5770372728174034</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.2211326875351351</v>
+        <v>0.1053667728442537</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6164</v>
+        <v>6285</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>379.5225993511317</v>
+        <v>372.9329532052843</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>12.4</v>
+        <v>230</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>48.26300874715489</v>
+        <v>42.46093498776879</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>31.65186780995611</v>
+        <v>22.68086867198395</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.577254236615266</v>
+        <v>1.209624947391127</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.0535348313385572</v>
+        <v>-1.472203857415822</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6290</v>
+        <v>6405</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>378.7077067609208</v>
+        <v>367.482338725216</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>241</v>
+        <v>40.45</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,49 +3361,49 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>37.92822112139577</v>
+        <v>48.88100527977116</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>22.45138752713562</v>
+        <v>11.42720932304584</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.8133622177079534</v>
+        <v>0.8040499993026722</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-5.14769966533054</v>
+        <v>-0.1525767164610537</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>avoid_chase, stronger_than_market, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6259</v>
+        <v>6185</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>378.402747701212</v>
+        <v>364.4134224833525</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>29.25</v>
+        <v>12.8</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>43.75573261784749</v>
+        <v>48.71126878500866</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>14.87684334004475</v>
+        <v>19.71376689412944</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.6373885306045443</v>
+        <v>0.5190079314417678</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.2644615531802973</v>
+        <v>0.02471207152306019</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6166</v>
+        <v>6174</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>370.3396473012074</v>
+        <v>362.1305553446718</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>103.5</v>
+        <v>49.3</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>29.04880107515773</v>
+        <v>46.96597950069045</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>24.0047378365571</v>
+        <v>17.75779138407032</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.4395881901848726</v>
+        <v>0.504251063292833</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-2.287462811909097</v>
+        <v>-0.9111276447059731</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6210</v>
+        <v>6187</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>368.7890260317168</v>
+        <v>359.8901219766541</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>18.85</v>
+        <v>1260</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>54.17252467864544</v>
+        <v>41.98032748303256</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>6.465254980870579</v>
+        <v>23.61668686202148</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.4978017104403912</v>
+        <v>0.6588398461457313</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.003570395000081</v>
+        <v>-28.88229394137132</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6244</v>
+        <v>6163</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>華電網</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>367.409709494459</v>
+        <v>358.1073475243682</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>21.2</v>
+        <v>40.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>39.33646448568697</v>
+        <v>42.34963721468672</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>15.17390356870842</v>
+        <v>20.04113878467574</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.7280176980431818</v>
+        <v>0.7065556234253727</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.1138734201430257</v>
+        <v>-0.3333043152307572</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6239</v>
+        <v>6467</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>泰合</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>362.440721806283</v>
+        <v>357.7256129865802</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>248</v>
+        <v>202.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>34.96580267011336</v>
+        <v>45.09504438757064</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>20.09652622903225</v>
+        <v>23.82667909218408</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.934941983401482</v>
+        <v>1.176351588861237</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-5.815837257695286</v>
+        <v>-6.293124571423642</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6224</v>
+        <v>6184</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>352.5453307429132</v>
+        <v>352.6703790402014</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>73.90000000000001</v>
+        <v>39.75</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>43.07001024896446</v>
+        <v>39.29259755407259</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>20.3118606267082</v>
+        <v>18.12821706298998</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.7271413870251814</v>
+        <v>0.9505886200777706</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.659503824872115</v>
+        <v>0.01006520375479891</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6462</v>
+        <v>6419</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>345.7006018832117</v>
+        <v>351.4581094225277</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>96.3</v>
+        <v>147</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>43.07267991640185</v>
+        <v>42.67162790447533</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>16.10236357880654</v>
+        <v>15.80925979190588</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.8213115440132339</v>
+        <v>0.720218977300666</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.6177699431046648</v>
+        <v>-1.450102454800556</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend</t>
+          <t>ema60_gt_ema120, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6409</v>
+        <v>6464</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>343.2818300350432</v>
+        <v>344.4212979615711</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>910</v>
+        <v>76</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>51.4760646127621</v>
+        <v>44.06658272241659</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>15.70882885187199</v>
+        <v>23.80406053988675</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.7153998161566312</v>
+        <v>0.3986958506219546</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>6.120000218036198</v>
+        <v>0.01881207816714953</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, cci_momentum, mfi_strong</t>
+          <t>avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6417</v>
+        <v>6441</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>342.2519713292631</v>
+        <v>342.5937962191653</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>97.3</v>
+        <v>21.45</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>33.00668846933881</v>
+        <v>41.08666675541784</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>27.51638197675785</v>
+        <v>12.00186828898663</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.513697526763331</v>
+        <v>0.3186330594557458</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.425220346884398</v>
+        <v>-0.194794316305846</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6472</v>
+        <v>6202</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>339.6272736044474</v>
+        <v>338.7687621748494</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>403</v>
+        <v>54.3</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>39.63647653892966</v>
+        <v>40.60047022560941</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>29.142004973221</v>
+        <v>12.96595014738856</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.7055078030690214</v>
+        <v>0.4458939642293094</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-1.921552467578645</v>
+        <v>-0.4713973299976539</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6435</v>
+        <v>6451</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>335.8955318291409</v>
+        <v>336.9260365936099</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>213</v>
+        <v>351</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>32.17204048691735</v>
+        <v>36.48514492491609</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>18.61855944424527</v>
+        <v>20.51815875354233</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.4418196652627401</v>
+        <v>0.7673668027537495</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-4.277029716435186</v>
+        <v>-4.996363063603033</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6274</v>
+        <v>6177</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>335.3092489921815</v>
+        <v>332.0092306554644</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>1420</v>
+        <v>45.25</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,49 +3997,49 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>39.74253347030256</v>
+        <v>40.93190921581994</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>19.82601705597462</v>
+        <v>9.750587254043181</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.730924899218151</v>
+        <v>0.4426821867782229</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M67" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-30.57943230398384</v>
+        <v>-0.02268243934997183</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, stronger_than_market, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6279</v>
+        <v>6282</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>326.1607602958402</v>
+        <v>328.483412616205</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>111.5</v>
+        <v>41.7</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>38.7471484296103</v>
+        <v>42.30688813253867</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>22.87808882565645</v>
+        <v>15.29926197787438</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.031704685850572</v>
+        <v>0.6291091592888773</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.1915744320977552</v>
+        <v>-0.1351173205114093</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6270</v>
+        <v>6423</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>316.7303568862035</v>
+        <v>326.9350622972959</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>27.9</v>
+        <v>82</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>37.16357540599985</v>
+        <v>43.57309485663201</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>16.87350929909756</v>
+        <v>15.28813049923044</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.6220159686264627</v>
+        <v>0.3142562496879532</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.2109864397269858</v>
+        <v>-0.8109780197796138</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6185</v>
+        <v>6265</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>309.4134224833525</v>
+        <v>324.4280184735206</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>12.8</v>
+        <v>43.9</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>48.71126881295343</v>
+        <v>32.03038264205276</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>19.71376691469811</v>
+        <v>24.49085421151782</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5190079314417678</v>
+        <v>0.58591246754207</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0247120715831467</v>
+        <v>-0.2211326876192501</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6236</v>
+        <v>6167</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>298.1668468197807</v>
+        <v>319.3242488835633</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>44.55140989113019</v>
+        <v>60.8538244503473</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>13.96089786001665</v>
+        <v>19.37674902823226</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0</v>
+        <v>0.8343576285214932</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-1.425587248397021</v>
+        <v>0.09831599355995868</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>rsi_strong, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6206</v>
+        <v>6290</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>297.8816705887378</v>
+        <v>318.7077067609208</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>127.5</v>
+        <v>241</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>34.91987954772705</v>
+        <v>37.92822107307615</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>12.9769619081735</v>
+        <v>22.45138754352809</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.8352331012409452</v>
+        <v>0.8133622177079534</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.8782033297344987</v>
+        <v>-5.147699664849853</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6419</v>
+        <v>6259</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>296.4581094225278</v>
+        <v>318.402747701212</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>147</v>
+        <v>29.25</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>42.67162789334767</v>
+        <v>43.75573262096812</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15.80925976031219</v>
+        <v>14.87684334603674</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.720218977300666</v>
+        <v>0.6373885306045443</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-1.45010245459628</v>
+        <v>-0.2644615532043315</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6284</v>
+        <v>6229</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>292.5910084003217</v>
+        <v>317.622669790989</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>72.5</v>
+        <v>23.2</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>39.68120859291368</v>
+        <v>42.54610965218362</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>13.5444082358834</v>
+        <v>14.49868882289624</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.8367183991488116</v>
+        <v>0.7337116262418329</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.4773424466350682</v>
+        <v>-0.06644144035911062</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6432</v>
+        <v>6239</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>289.6523911358621</v>
+        <v>317.4407218062833</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>58.1</v>
+        <v>248</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>42.40987572301896</v>
+        <v>34.96580266540288</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>18.66631831917365</v>
+        <v>20.09652617965135</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.2388615937016738</v>
+        <v>0.934941983401482</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.6066177946077824</v>
+        <v>-5.815837257575128</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6464</v>
+        <v>6176</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>289.4212979615711</v>
+        <v>315.4753002505907</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>76</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>44.0665827802945</v>
+        <v>46.2357764095016</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>23.80406058468414</v>
+        <v>9.103864300988578</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.3986958506219546</v>
+        <v>1.560135065854949</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0188120781431005</v>
+        <v>-0.1214513120895138</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>volume_break, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6261</v>
+        <v>6228</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>288.088647421103</v>
+        <v>314.98501651955</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>73.09999999999999</v>
+        <v>16.85</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>36.33721908058625</v>
+        <v>52.22630981074426</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>11.89911398957909</v>
+        <v>13.04338907658055</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.7088647421102982</v>
+        <v>0.4506725487651918</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.6654665394959525</v>
+        <v>-0.4440891499067408</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6414</v>
+        <v>6281</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>286.9047367228868</v>
+        <v>311.9804891749344</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>377.5</v>
+        <v>50.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>41.0410635733919</v>
+        <v>38.12016307802378</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>14.54458383170573</v>
+        <v>6.852570144367955</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5793334974259351</v>
+        <v>2.427258755264709</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-1.794214875142197</v>
+        <v>-0.02594204657897616</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6202</v>
+        <v>6411</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>283.7687621748493</v>
+        <v>308.8541683362196</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>54.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>40.60047032499686</v>
+        <v>37.21330452121752</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>12.96595012223193</v>
+        <v>9.465805361857504</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.4458939642293094</v>
+        <v>0.9879476334987756</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.4713973301538784</v>
+        <v>-0.268027523786165</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6189</v>
+        <v>6183</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>280.8907140876715</v>
+        <v>304.7488614403353</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>48.2</v>
+        <v>91</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>42.72261131752207</v>
+        <v>48.09318554494792</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>19.44028211378373</v>
+        <v>15.26455533968555</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.6455369966166463</v>
+        <v>0.6080695334232654</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.2127286599729317</v>
+        <v>-0.06866616039812959</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6182</v>
+        <v>6266</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>277.3264838692383</v>
+        <v>287.5920706282302</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>104.5</v>
+        <v>24.75</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>40.68829056311731</v>
+        <v>42.2626352290009</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>19.30406041604122</v>
+        <v>13.4820941020908</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.3277851763556027</v>
+        <v>0.5314520845681304</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-2.662322785749595</v>
+        <v>-0.131168746574325</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6223</v>
+        <v>6417</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>275.1517507111494</v>
+        <v>282.2519713292633</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>4890</v>
+        <v>97.3</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,49 +4792,49 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>39.87430343899285</v>
+        <v>33.00668851463618</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>16.0726910497991</v>
+        <v>27.51638197675785</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.732448737896305</v>
+        <v>1.513697526763331</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-75.60938775332372</v>
+        <v>-0.4252203472449203</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6423</v>
+        <v>6472</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>271.935062297296</v>
+        <v>279.6272736044474</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>43.57309478538095</v>
+        <v>39.63647650673768</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>15.28813049654464</v>
+        <v>29.14200501989702</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3142562496879532</v>
+        <v>0.7055078030690214</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.8109780195392575</v>
+        <v>-1.92155246902073</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6165</v>
+        <v>6435</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>270.1841637473945</v>
+        <v>275.8955318291406</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>48.65</v>
+        <v>213</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>49.63021916592513</v>
+        <v>32.17204048878885</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>13.52333645336955</v>
+        <v>18.61855943002146</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.5770372728174034</v>
+        <v>0.4418196652627401</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.105366772700042</v>
+        <v>-4.277029716987982</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6441</v>
+        <v>6274</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>262.5937962191653</v>
+        <v>275.3092489921815</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>21.45</v>
+        <v>1420</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>41.08666681952951</v>
+        <v>39.74253342036971</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>12.00186830089442</v>
+        <v>19.82601702725682</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.3186330594557457</v>
+        <v>1.730924899218151</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.1947943163298821</v>
+        <v>-30.57943229977781</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, volume_break, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6176</v>
+        <v>6208</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>260.4753002505906</v>
+        <v>266.4868197135004</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>90.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>46.23577671615089</v>
+        <v>38.50361059488515</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>9.103864280368422</v>
+        <v>16.77364682839044</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.560135065854949</v>
+        <v>0.6177546508757084</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.1214513122954582</v>
+        <v>-0.3803953203069896</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6281</v>
+        <v>6279</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>256.9804891749388</v>
+        <v>266.1607602958402</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>50.5</v>
+        <v>111.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>38.12016307802378</v>
+        <v>38.74714828117263</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>6.852570100860199</v>
+        <v>22.87808888526706</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>2.427258755264709</v>
+        <v>1.031704685850572</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.0259420465549367</v>
+        <v>-0.1915744317372401</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6188</v>
+        <v>6443</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>256.8052914312745</v>
+        <v>257.774819400156</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>40.18137521777589</v>
+        <v>48.15529524225773</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>21.93048351293871</v>
+        <v>19.7107992943572</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.02958028798918</v>
+        <v>1.649037471566105</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0560954111146522</v>
+        <v>-0.1667650627196914</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>volume_break, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6411</v>
+        <v>6270</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>253.8541683362194</v>
+        <v>256.7303568862035</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>74.09999999999999</v>
+        <v>27.9</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>37.2133044419842</v>
+        <v>37.1635754371842</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>9.465805433866825</v>
+        <v>16.87350913251257</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.9879476334987756</v>
+        <v>0.6220159686264627</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.2680275235938891</v>
+        <v>-0.2109864397510212</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6229</v>
+        <v>6216</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>237.6226697909854</v>
+        <v>244.363436335732</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>23.2</v>
+        <v>19.2</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>42.54611001714556</v>
+        <v>40.77252138030745</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>14.49868861034079</v>
+        <v>21.96379934198058</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.7337116262418329</v>
+        <v>0.4918371564372804</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.06644144052735659</v>
+        <v>-0.0155764033596959</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6266</v>
+        <v>6236</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>中湛</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>232.5920706282301</v>
+        <v>238.1668468197807</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>24.75</v>
+        <v>0</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>42.26263511932205</v>
+        <v>44.55140989863094</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>13.48209412718094</v>
+        <v>13.96089785711258</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5314520845681304</v>
+        <v>0</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.1311687465983587</v>
+        <v>-1.425587248421056</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6230</v>
+        <v>6206</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>231.7389777375777</v>
+        <v>237.8816705887379</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>108</v>
+        <v>127.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>43.07968361638804</v>
+        <v>34.91987974041824</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>16.12535509434688</v>
+        <v>12.97696194553589</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.491893028793488</v>
+        <v>0.8352331012409452</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.5333153714571501</v>
+        <v>-0.8782033300950001</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6183</v>
+        <v>6215</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>229.7488614403352</v>
+        <v>234.2400448020725</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>91</v>
+        <v>89.2</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>48.09318554494792</v>
+        <v>35.12404507175991</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>15.26455510814652</v>
+        <v>17.93071925057663</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.6080695334232654</v>
+        <v>0.9621708467024712</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.0686661602779558</v>
+        <v>-0.4948365691088927</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6442</v>
+        <v>6284</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>211.7663236061506</v>
+        <v>232.5910084003217</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>1410</v>
+        <v>72.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>39.04530024985825</v>
+        <v>39.68120852153761</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>18.20537898476872</v>
+        <v>13.54440823327485</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.6093792743911375</v>
+        <v>0.8367183991488116</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-25.85459689769063</v>
+        <v>-0.4773424464668279</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6208</v>
+        <v>6432</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>211.4868197135005</v>
+        <v>229.6523911358621</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>72.3</v>
+        <v>58.1</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>38.5036106330428</v>
+        <v>42.40987571441958</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>16.7736467540094</v>
+        <v>18.66631841803529</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.6177546508757084</v>
+        <v>0.2388615937016738</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.3803953202829353</v>
+        <v>-0.6066177946077824</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6167</v>
+        <v>6261</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>209.3242488835633</v>
+        <v>228.088647421103</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>10.9</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>60.85382478537641</v>
+        <v>36.33721909298977</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>19.37674911301301</v>
+        <v>11.89911395834071</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.8343576285214932</v>
+        <v>0.7088647421102982</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.09831599359525631</v>
+        <v>-0.6654665395920856</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6443</v>
+        <v>6414</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>192.7748194001564</v>
+        <v>226.9047367228868</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>26</v>
+        <v>377.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>48.15529524597315</v>
+        <v>41.04106358117504</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>19.71079938383527</v>
+        <v>14.54458384347341</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.649037471566105</v>
+        <v>0.5793334974259351</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.1667650626235506</v>
+        <v>-1.794214876103579</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6184</v>
+        <v>6189</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>187.6703790402014</v>
+        <v>220.8907140876711</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>39.75</v>
+        <v>48.2</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>39.29259768322682</v>
+        <v>42.72261137385655</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>18.12821706298998</v>
+        <v>19.4402820444486</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.9505886200777706</v>
+        <v>0.6455369966166463</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.0100652037307665</v>
+        <v>-0.2127286602613465</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6275</v>
+        <v>6182</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>186.0385690484506</v>
+        <v>217.3264838692384</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>44.5</v>
+        <v>104.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>39.42928401787199</v>
+        <v>40.68829055885323</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>21.49564497334273</v>
+        <v>19.30406044905748</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.235452198499643</v>
+        <v>0.3277851763556027</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.2875912623393788</v>
+        <v>-2.662322785809681</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6217</v>
+        <v>6223</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>183.0169839828917</v>
+        <v>215.1517507111491</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>159</v>
+        <v>4890</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,49 +5746,49 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>41.00225271004447</v>
+        <v>39.87430339923723</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>18.92605793504876</v>
+        <v>16.07269091723709</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.501698398289172</v>
+        <v>0.732448737896305</v>
       </c>
       <c r="K100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L100" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M100" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-2.423439908980588</v>
+        <v>-75.60938772808734</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6215</v>
+        <v>6235</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>179.2400448020727</v>
+        <v>213.992578252269</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>89.2</v>
+        <v>35.45</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>35.1240454285811</v>
+        <v>36.64448632843487</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>17.93071920692884</v>
+        <v>16.00795412429219</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.9621708467024712</v>
+        <v>0.5427307671178602</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.4948365698299273</v>
+        <v>-0.1323493480862767</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6161</v>
+        <v>6243</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>捷波</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>176.1812168088304</v>
+        <v>210.244300848079</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>45.7</v>
+        <v>36.55</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>31.76191441704258</v>
+        <v>41.74412485819607</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>11.60455408473611</v>
+        <v>16.10483769542439</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.186004476211294</v>
+        <v>0.4215792906941168</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.2726743075476465</v>
+        <v>-0.1021127027909715</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6228</v>
+        <v>6220</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>174.98501651955</v>
+        <v>197.8398913660592</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>16.85</v>
+        <v>25</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>52.22630984285863</v>
+        <v>38.75829517534873</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>13.04338910149003</v>
+        <v>12.03675796292755</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.4506725487651918</v>
+        <v>0.4552798044629044</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.4440891498346371</v>
+        <v>0.01326404873958562</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, mfi_strong, above_ichimoku_cloud</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6222</v>
+        <v>6188</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>166.2281384094426</v>
+        <v>196.8052914312745</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>18.5</v>
+        <v>61</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>49.17189696454592</v>
+        <v>40.18137479973824</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>6.537717252259723</v>
+        <v>21.9304835296479</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.762763858258577</v>
+        <v>1.02958028798918</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0290794320807532</v>
+        <v>0.05609541111465222</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6216</v>
+        <v>6272</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>164.3634363357319</v>
+        <v>171.8923795645469</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>19.2</v>
+        <v>23.2</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>40.77252146117562</v>
+        <v>37.01438917751854</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>21.96379941257171</v>
+        <v>18.16633910633625</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.4918371564372804</v>
+        <v>1.173065588498997</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0155764033356615</v>
+        <v>-0.1595868411806254</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6177</v>
+        <v>6230</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>162.0092306554645</v>
+        <v>171.738977737577</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>45.25</v>
+        <v>108</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>40.93190910910207</v>
+        <v>43.0796834240035</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>9.750587256083731</v>
+        <v>16.12535511014446</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.4426821867782229</v>
+        <v>1.491893028793488</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0226824393980337</v>
+        <v>-0.5333153709764629</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6243</v>
+        <v>6283</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>155.244300848079</v>
+        <v>169.2256788464271</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>36.55</v>
+        <v>18.9</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>41.74412483528241</v>
+        <v>47.70824979176303</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>16.10483764781213</v>
+        <v>11.32705224788188</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.4215792906941168</v>
+        <v>0.7033086634740966</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.1021127025386091</v>
+        <v>0.06779734638887819</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6220</v>
+        <v>6442</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>142.8398913660547</v>
+        <v>151.7663236061505</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>25</v>
+        <v>1410</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>38.75829515589304</v>
+        <v>39.04530017218787</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>12.03675806094646</v>
+        <v>18.20537904403647</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.4552798044629044</v>
+        <v>0.6093792743911375</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0132640487516018</v>
+        <v>-25.85459688399067</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6405</v>
+        <v>6237</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>142.482338725216</v>
+        <v>136.2855693354552</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>40.45</v>
+        <v>32.25</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>48.88100532049104</v>
+        <v>38.0311444233766</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>11.42720928023898</v>
+        <v>18.87114521283742</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.8040499993026722</v>
+        <v>0.2637962126132823</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.152576716533154</v>
+        <v>-0.2893208648187467</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6412</v>
+        <v>6275</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>117.8873197944741</v>
+        <v>126.0385690484506</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>72.3</v>
+        <v>44.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>35.16830355937707</v>
+        <v>39.42928373469721</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>15.57303901424878</v>
+        <v>21.49564502326353</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.155096072214059</v>
+        <v>1.235452198499643</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0650482293868361</v>
+        <v>-0.2875912621471023</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6272</v>
+        <v>6217</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>111.8923795645469</v>
+        <v>123.0169839828917</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>23.2</v>
+        <v>159</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>37.01438792149469</v>
+        <v>41.00225268692087</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>18.1663391114813</v>
+        <v>18.92605785373228</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.173065588498997</v>
+        <v>0.501698398289172</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.1595868412286971</v>
+        <v>-2.423439907959115</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6203</v>
+        <v>6161</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>捷波</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>100.4528978359756</v>
+        <v>116.1812168088303</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>56.5</v>
+        <v>45.7</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>22.82307708673187</v>
+        <v>31.76191439235775</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>16.14584124389782</v>
+        <v>11.60455401121164</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.6973022282200585</v>
+        <v>1.186004476211294</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.2827038228781608</v>
+        <v>-0.2726743076077329</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6283</v>
+        <v>6222</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>89.22567884642713</v>
+        <v>106.2281384094418</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>47.7082502626299</v>
+        <v>49.17189697070339</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>11.32705231599201</v>
+        <v>6.53771727056706</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.7033086634740966</v>
+        <v>0.762763858258577</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0677973464850202</v>
+        <v>0.02907943209277046</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6276</v>
+        <v>6412</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>81.31005534658613</v>
+        <v>57.88731979447381</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>17.95</v>
+        <v>72.3</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>48.51248974513938</v>
+        <v>35.16830352376803</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>9.310230011423618</v>
+        <v>15.57303903348749</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.1556555978811548</v>
+        <v>1.155096072214059</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.08810602401595841</v>
+        <v>0.06504822902631313</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6237</v>
+        <v>6203</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>海韻電</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>81.28556933545546</v>
+        <v>40.45289783597476</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>32.25</v>
+        <v>56.5</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>38.0311446148684</v>
+        <v>22.82307696936611</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>18.8711451854074</v>
+        <v>16.14584122399383</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.2637962126132823</v>
+        <v>0.6973022282200585</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.2893208650230437</v>
+        <v>-0.2827038228541241</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6235</v>
+        <v>6276</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>安鈦克</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>48.99257825226843</v>
+        <v>21.31005534658614</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>35.45</v>
+        <v>17.95</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>36.64448627164003</v>
+        <v>48.5124896867868</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>16.00795417684686</v>
+        <v>9.310229972946777</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.5427307671178602</v>
+        <v>0.1556555978811549</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,11 +6612,11 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.132349347918035</v>
+        <v>0.08810602397990547</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase</t>
         </is>
       </c>
     </row>

--- a/output/full_scan/batch_seq6_2026-10-22.xlsx
+++ b/output/full_scan/batch_seq6_2026-10-22.xlsx
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>78.90131148220883</v>
+        <v>78.90131156175438</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>33.15849057183254</v>
+        <v>33.15849061754602</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.887832827195892</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1917634644417778</v>
+        <v>0.1917634640524146</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>88.80743659518778</v>
+        <v>88.80743663051797</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>40.42124230723691</v>
+        <v>40.42124236999416</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>4.685271930498494</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>2.338155083939738</v>
+        <v>2.338155083809959</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>67.03613213401631</v>
+        <v>67.03613243533684</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>19.45238165251561</v>
+        <v>19.45238169571356</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>2.026592574560778</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.04737782222289627</v>
+        <v>0.04737782209310933</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>65.64072220204432</v>
+        <v>65.6407222068942</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>34.890155062347</v>
+        <v>34.89015513951923</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>2.416036974209795</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.3201726229756376</v>
+        <v>-0.3201726229496833</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>55.08568304782916</v>
+        <v>55.0856830495019</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>36.65148666452099</v>
+        <v>36.65148684351382</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>1.233027650764054</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-5.186169113455673</v>
+        <v>-5.186169113878286</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>857.237312605263</v>
+        <v>857.2373126052629</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>90.09999999999999</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>60.41895108188609</v>
+        <v>60.41895069619824</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>33.02733244354248</v>
+        <v>33.02733246566626</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1.281559472437751</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.02741526892322721</v>
+        <v>0.02741526840408426</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>54.64295262449493</v>
+        <v>54.64295263835304</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>33.47085422785257</v>
+        <v>33.47085421456798</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>0.6145525805647692</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.6052151002842892</v>
+        <v>-0.6052151005438731</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>66.14815018164282</v>
+        <v>66.14815023444106</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>33.13629603199323</v>
+        <v>33.13629602100019</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>2.544511166061138</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.7480122025300724</v>
+        <v>0.7480122021666666</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>60.06618486530025</v>
+        <v>60.06618490310662</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>49.94953713038884</v>
+        <v>49.94953734204721</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>1.398229788631511</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1.547504951229226</v>
+        <v>1.547504950749008</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>59.64192345871853</v>
+        <v>59.64192344313563</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>26.41004630783667</v>
+        <v>26.41004659100323</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>3.166044129630837</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>2.003902512995683</v>
+        <v>2.003902512580358</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>712.1949567710934</v>
+        <v>712.1949567710933</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>26.85</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>82.00485215658971</v>
+        <v>82.00485241673489</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>52.30388539492535</v>
+        <v>52.30388558433571</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>2.033008627467827</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.2300014572477103</v>
+        <v>0.2300014569881352</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>49.94045097420253</v>
+        <v>49.94045106699661</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>36.37853756754624</v>
+        <v>36.37853757561509</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>0.6998040680600051</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.9585343456074904</v>
+        <v>-0.9585343487223748</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>677.0219967973202</v>
+        <v>677.0219967973212</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>45.9</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>68.14931605877572</v>
+        <v>68.14931598112399</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>35.44148197183497</v>
+        <v>35.44148194933189</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>0.6476559223050367</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.2317171874937166</v>
+        <v>0.2317171873639329</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>69.44974521961467</v>
+        <v>69.44974491603531</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>41.35617004318013</v>
+        <v>41.35617015557782</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>5.971524141804417</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.07751029843398038</v>
+        <v>0.07751029840802381</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>64.81172466953879</v>
+        <v>64.81172467745395</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>51.30590219839804</v>
+        <v>51.3059022253042</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>1.252859594182261</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>3.795119548270154</v>
+        <v>3.795119547750986</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>53.90440080384538</v>
+        <v>53.90440152316441</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>28.80512445100012</v>
+        <v>28.80512429673319</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>0.6183082921517314</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.102891322796602</v>
+        <v>0.1028913194221461</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>42.48192274653715</v>
+        <v>42.48192271990463</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>30.04794274966148</v>
+        <v>30.04794246560368</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0.2501599396096814</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-1.291802676947541</v>
+        <v>-1.291802676415414</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>619.4782183600228</v>
+        <v>619.4782183600238</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>472</v>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>55.82687224204486</v>
+        <v>55.82687234176015</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>22.08385971397313</v>
+        <v>22.08385990619946</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>1.865041219778342</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>4.10893205517692</v>
+        <v>4.108932051413049</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>610.6013962923112</v>
+        <v>610.6013962923113</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>50</v>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>61.7646697223823</v>
+        <v>61.76466998866634</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>25.2116578831926</v>
+        <v>25.21165818000409</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>1.140741378769861</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.07249027042325401</v>
+        <v>0.07249027016367782</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>50.40165483345383</v>
+        <v>50.40165487128143</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>26.14804709642917</v>
+        <v>26.14804729550728</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>0.5791253972083167</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-1.693799943306909</v>
+        <v>-1.693799944578823</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>577.4650523533123</v>
+        <v>577.4650523533122</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>597</v>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>50.72621450008403</v>
+        <v>50.72621446759339</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>31.53902368895329</v>
+        <v>31.53902381118123</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>0.4832205599883757</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-8.311415719534434</v>
+        <v>-8.311415718366369</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>571.9514534984928</v>
+        <v>571.9514534984929</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>19.55</v>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>52.29308520893061</v>
+        <v>52.29308520366342</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>7.38586692747694</v>
+        <v>7.385866887955562</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>0.9435408730111927</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.3680997728875546</v>
+        <v>0.368099772991384</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>571.7477354972317</v>
+        <v>571.7477354972316</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>232</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>42.43749228234979</v>
+        <v>42.43749229197072</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>28.93118720321106</v>
+        <v>28.93118721219972</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>0.5603887573874565</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-5.813970493924819</v>
+        <v>-5.813970494418005</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>60.52530551074071</v>
+        <v>60.52530552710639</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>31.63464733604794</v>
+        <v>31.63464738002723</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>2.53425075941183</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-5.099216836016609</v>
+        <v>-5.099216838482505</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>66.95384630257544</v>
+        <v>66.95384635554649</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>36.24106969199593</v>
+        <v>36.24106969201431</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>13.57004154429711</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1.280897501275817</v>
+        <v>1.280897501444539</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>558.1509004929644</v>
+        <v>558.1509004929636</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>115</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>58.25200564476405</v>
+        <v>58.25200599885891</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>23.8649010645223</v>
+        <v>23.86490113444244</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>1.29480849990638</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.46874137484461</v>
+        <v>0.4687413739361129</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>548.2128851983215</v>
+        <v>548.2128851983216</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>41.85</v>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>43.48960106896989</v>
+        <v>43.48960113609603</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>21.20336229737828</v>
+        <v>21.20336236407856</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>2.152664272709147</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.4155686625625881</v>
+        <v>0.415568662340154</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>43.96007259048138</v>
+        <v>43.96007258936589</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>36.05988863148296</v>
+        <v>36.0598886415957</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>0.5113305909110898</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-1.20503810805427</v>
+        <v>-1.205038108072437</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>45.18736472900692</v>
+        <v>45.18736474461694</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>22.21152687383203</v>
+        <v>22.21152693855917</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>0.7864727676954077</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-6.192578774217576</v>
+        <v>-6.192578775255869</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>43.41363655403386</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>20.82924988418803</v>
+        <v>20.82925010494149</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>0.1866793272497344</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.7767470553439226</v>
+        <v>-0.7767470555385939</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>493.2204727641994</v>
+        <v>493.2204727641995</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>104.5</v>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>50.04581624807792</v>
+        <v>50.04581625924752</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>24.01983924377861</v>
+        <v>24.01983942891731</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>0.4830325583215399</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-1.378983245600434</v>
+        <v>-1.378983244925559</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>56.53966589481185</v>
+        <v>56.53966589134033</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>31.24587084498942</v>
+        <v>31.24587078004762</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0.3407759209715591</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.1250449838521526</v>
+        <v>0.1250449840208798</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>487.2097275784325</v>
+        <v>487.2097275784323</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>46</v>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>57.32572715890439</v>
+        <v>57.32572722921451</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>40.65618556437843</v>
+        <v>40.65618557774729</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0.8579285059578369</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.1599100456371082</v>
+        <v>0.1599100455332787</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>43.43573046159274</v>
+        <v>43.43573050919412</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>10.92814114056611</v>
+        <v>10.92814117291418</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>0.6308991060770219</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>3.220756256699413</v>
+        <v>3.220756256180326</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>41.01842364847722</v>
+        <v>41.01842365791195</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>22.25653640119004</v>
+        <v>22.25653663076563</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>0.7881131899594851</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-3.016949127973012</v>
+        <v>-3.016949128362338</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>45.64879485948919</v>
+        <v>45.64879488325099</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>26.36145669580239</v>
+        <v>26.36145686716847</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>0.6606877362996376</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.5764223441692444</v>
+        <v>-0.5764223443898869</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>44.38903008910564</v>
+        <v>44.38903008640304</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>24.47871259229134</v>
+        <v>24.47871251068761</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>0.4188212073909783</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-1.497159607456259</v>
+        <v>-1.497159607495197</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>51.99799419613434</v>
+        <v>51.9979942215828</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>28.03045116843188</v>
+        <v>28.03045122781381</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>0.8073056122401421</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.3724378738241652</v>
+        <v>-0.3724378742135421</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>451.6897327308894</v>
+        <v>451.6897327308895</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>317</v>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>43.03512729454533</v>
+        <v>43.03512732561887</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>22.96535417764487</v>
+        <v>22.96535419368785</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>0.743549978550329</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-5.526473731241047</v>
+        <v>-5.526473732019731</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>448.7890260317169</v>
+        <v>448.789026031717</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>18.85</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>54.17252468642187</v>
+        <v>54.17252476598073</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>6.465255335144739</v>
+        <v>6.465255837183021</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>0.4978017104403912</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.003570395288495787</v>
+        <v>-0.003570395574027052</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>30.97607550061628</v>
+        <v>30.97607562471484</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>29.10603318326356</v>
+        <v>29.1060332513963</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>0.4070879222902932</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-11.86443332235417</v>
+        <v>-11.864433325469</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>443.2818300350433</v>
+        <v>443.2818300350431</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>910</v>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.47606461986035</v>
+        <v>51.47606460457181</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>15.70882893857922</v>
+        <v>15.70882899671447</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>0.7153998161566312</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>6.120000213229346</v>
+        <v>6.120000208557011</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>43.07001023667062</v>
+        <v>43.07001024196642</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>20.31186054987297</v>
+        <v>20.31186077810607</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>0.7271413870251814</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.6595038249322008</v>
+        <v>-0.6595038251268825</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>425.7006018832118</v>
+        <v>425.7006018832119</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>96.3</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>43.07267987866539</v>
+        <v>43.07267998026353</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>16.10236338725004</v>
+        <v>16.10236348642621</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>0.8213115440132339</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.6177699439458755</v>
+        <v>-0.6177699451139422</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>29.0488010639813</v>
+        <v>29.04880106999937</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>24.00473785967107</v>
+        <v>24.0047379485804</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.4395881901848726</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-2.287462812053302</v>
+        <v>-2.287462812416705</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>422.409709494459</v>
+        <v>422.4097094944597</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>21.2</v>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>39.33646446054198</v>
+        <v>39.33646449845289</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>15.1739034166078</v>
+        <v>15.17390352224302</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.7280176980431818</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.1138734202031115</v>
+        <v>-0.1138734203328983</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>419.5225993511321</v>
+        <v>419.5225993511318</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>12.4</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>48.26300861798374</v>
+        <v>48.26300868512116</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>31.6518677951872</v>
+        <v>31.65186784950163</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>1.577254236615266</v>
@@ -3008,7 +3008,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.05353483125443645</v>
+        <v>-0.05353483134528794</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3043,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>40.20477865001131</v>
+        <v>40.20477836627167</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>25.52246550091668</v>
+        <v>25.52246566965961</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0.4165843898479347</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-2.115153760662388</v>
+        <v>-2.115153758404115</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>43.6231682260992</v>
+        <v>43.62316828151636</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>21.6859000493734</v>
+        <v>21.68590023469326</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>0.5971790049014803</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-1.982313014288239</v>
+        <v>-1.982313017273315</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>390.3716792665684</v>
+        <v>390.3716792665695</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>66.40000000000001</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>36.51630034547541</v>
+        <v>36.5163003784789</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>17.05801338360466</v>
+        <v>17.05801356902393</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>0.6658116057695529</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.7485696728379544</v>
+        <v>-0.7485696732402938</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>387.7442054053454</v>
+        <v>387.7442054053459</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>64.7</v>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>35.69826603924925</v>
+        <v>35.69826600268608</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>22.2042564816358</v>
+        <v>22.20425659630393</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>0.6613033381130128</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-1.095400227601492</v>
+        <v>-1.095400227653411</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>49.63021911942405</v>
+        <v>49.63021895151141</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>13.52333650413539</v>
+        <v>13.52333661687568</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.5770372728174034</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.1053667728442537</v>
+        <v>0.1053667728702124</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>42.46093498776879</v>
+        <v>42.46093502926755</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>22.68086867198395</v>
+        <v>22.68086874762121</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>1.209624947391127</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-1.472203857415822</v>
+        <v>-1.472203858713728</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>48.88100527977116</v>
+        <v>48.88100525967484</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>11.42720932304584</v>
+        <v>11.42720954479049</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>0.8040499993026722</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.1525767164610537</v>
+        <v>-0.1525767165778569</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>48.71126878500866</v>
+        <v>48.71126886024458</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>19.71376689412944</v>
+        <v>19.71376691315064</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>0.5190079314417678</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.02471207152306019</v>
+        <v>0.02471207143220994</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>362.1305553446718</v>
+        <v>362.1305553446717</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>49.3</v>
@@ -3470,7 +3470,7 @@
         <v>46.96597950069045</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>17.75779138407032</v>
+        <v>17.75779143753459</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>0.504251063292833</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.9111276447059731</v>
+        <v>-0.9111276447319314</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>359.8901219766541</v>
+        <v>359.8901219766542</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>1260</v>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>41.98032748303256</v>
+        <v>41.9803274788225</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>23.61668686202148</v>
+        <v>23.61668679874655</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>0.6588398461457313</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-28.88229394137132</v>
+        <v>-28.88229394266896</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>358.1073475243682</v>
+        <v>358.1073475243697</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>40.5</v>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>42.34963721468672</v>
+        <v>42.3496372319269</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>20.04113878467574</v>
+        <v>20.04113881620643</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>0.7065556234253727</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.3333043152307572</v>
+        <v>-0.3333043153864979</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>45.09504438757064</v>
+        <v>45.09504446452429</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>23.82667909218408</v>
+        <v>23.82667916190858</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>1.176351588861237</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>39.29259755407259</v>
+        <v>39.2925975933078</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>18.12821706298998</v>
+        <v>18.12821706449261</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>0.9505886200777706</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.01006520375479891</v>
+        <v>0.01006520370288294</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>42.67162790447533</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>15.80925979190588</v>
+        <v>15.80925978272022</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>0.720218977300666</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-1.450102454800556</v>
+        <v>-1.450102454787583</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>44.06658272241659</v>
+        <v>44.06658278474664</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>23.80406053988675</v>
+        <v>23.80406055080532</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>0.3986958506219546</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.01881207816714953</v>
+        <v>0.0188120780633162</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>342.5937962191653</v>
+        <v>342.5937962191654</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>21.45</v>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>41.08666675541784</v>
+        <v>41.08666673932102</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>12.00186828898663</v>
+        <v>12.0018683298396</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>0.3186330594557458</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.194794316305846</v>
+        <v>-0.1947943164356323</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>338.7687621748494</v>
+        <v>338.7687621748493</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>54.3</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>40.60047022560941</v>
+        <v>40.60047027464629</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>12.96595014738856</v>
+        <v>12.96595018636582</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.4458939642293094</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.4713973299976539</v>
+        <v>-0.4713973303740281</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>36.48514492491609</v>
+        <v>36.48514494369422</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>20.51815875354233</v>
+        <v>20.51815889733559</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>0.7673668027537495</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-4.996363063603033</v>
+        <v>-4.996363064771156</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>332.0092306554644</v>
+        <v>332.0092306554643</v>
       </c>
       <c r="E67" s="2" t="n">
         <v>45.25</v>
@@ -4000,7 +4000,7 @@
         <v>40.93190921581994</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>9.750587254043181</v>
+        <v>9.750587199300613</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>0.4426821867782229</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.02268243934997183</v>
+        <v>-0.02268243914230822</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>328.483412616205</v>
+        <v>328.4834126162063</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>41.7</v>
@@ -4050,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>42.30688813253867</v>
+        <v>42.30688816675527</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15.29926197787438</v>
+        <v>15.29926213219526</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>0.6291091592888773</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.1351173205114093</v>
+        <v>-0.1351173207320366</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>43.57309485663201</v>
+        <v>43.57309476926993</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>15.28813049923044</v>
+        <v>15.28813054035275</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>0.3142562496879532</v>
@@ -4121,7 +4121,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.8109780197796138</v>
+        <v>-0.8109780195459975</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>32.03038264205276</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>24.49085421151782</v>
+        <v>24.49085424502265</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.58591246754207</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.2211326876192501</v>
+        <v>-0.2211326876452091</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>60.8538244503473</v>
+        <v>60.85382488330799</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>19.37674902823226</v>
+        <v>19.37674930391606</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>0.8343576285214932</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.09831599355995868</v>
+        <v>0.09831599333123497</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>37.92822107307615</v>
+        <v>37.92822110967214</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>22.45138754352809</v>
+        <v>22.45138767198857</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>0.8133622177079534</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-5.147699664849853</v>
+        <v>-5.147699666147743</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4315,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>43.75573262096812</v>
+        <v>43.7557326243288</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>14.87684334603674</v>
+        <v>14.87684339446275</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>0.6373885306045443</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.2644615532043315</v>
+        <v>-0.2644615532173088</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>317.622669790989</v>
+        <v>317.6226697909884</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>23.2</v>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>42.54610965218362</v>
+        <v>42.54610963574236</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>14.49868882289624</v>
+        <v>14.49868891398552</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>0.7337116262418329</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.06644144035911062</v>
+        <v>-0.06644144042400554</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>34.96580266540288</v>
+        <v>34.96580267047571</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>20.09652617965135</v>
+        <v>20.09652617979782</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>0.934941983401482</v>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>46.2357764095016</v>
+        <v>46.23577657025787</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>9.103864300988578</v>
+        <v>9.103864503199361</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>1.560135065854949</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.1214513120895138</v>
+        <v>-0.1214513132016611</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>52.22630981074426</v>
+        <v>52.22630981911153</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>13.04338907658055</v>
+        <v>13.04338897257761</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0.4506725487651918</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.4440891499067408</v>
+        <v>-0.444089150789291</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>311.9804891749344</v>
+        <v>311.9804891749366</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>50.5</v>
@@ -4580,7 +4580,7 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>38.12016307802378</v>
+        <v>38.12016304578459</v>
       </c>
       <c r="I78" s="2" t="n">
         <v>6.852570144367955</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.02594204657897616</v>
+        <v>-0.02594204660493094</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>37.21330452121752</v>
+        <v>37.21330444108085</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>9.465805361857504</v>
+        <v>9.465805422527808</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>0.9879476334987756</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.268027523786165</v>
+        <v>-0.2680275236563803</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>48.09318554494792</v>
+        <v>48.09318561686796</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>15.26455533968555</v>
+        <v>15.26455533280837</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>0.6080695334232654</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.06866616039812959</v>
+        <v>-0.06866616052791649</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>42.2626352290009</v>
+        <v>42.26263508135629</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>13.4820941020908</v>
+        <v>13.48209430188449</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>0.5314520845681304</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.131168746574325</v>
+        <v>-0.1311687464445384</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>282.2519713292633</v>
+        <v>282.251971329263</v>
       </c>
       <c r="E82" s="2" t="n">
         <v>97.3</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>33.00668851463618</v>
+        <v>33.0066884658544</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>27.51638197675785</v>
+        <v>27.51638200017733</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>1.513697526763331</v>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>39.63647650673768</v>
+        <v>39.636476738601</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>29.14200501989702</v>
+        <v>29.14200504635948</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>0.7055078030690214</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-1.92155246902073</v>
+        <v>-1.92155247161646</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>275.8955318291406</v>
+        <v>275.8955318291405</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>213</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>32.17204048878885</v>
+        <v>32.17204049819425</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>18.61855943002146</v>
+        <v>18.61855957768476</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>0.4418196652627401</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-4.277029716987982</v>
+        <v>-4.277029717507125</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>39.74253342036971</v>
+        <v>39.7425334334281</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>19.82601702725682</v>
+        <v>19.82601724467363</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>1.730924899218151</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-30.57943229977781</v>
+        <v>-30.57943230678627</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>266.4868197135004</v>
+        <v>266.4868197135008</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>72.3</v>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>38.50361059488515</v>
+        <v>38.50361059945103</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>16.77364682839044</v>
+        <v>16.77364683899512</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>0.6177546508757084</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.3803953203069896</v>
+        <v>-0.3803953205665522</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>38.74714828117263</v>
+        <v>38.74714832246571</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>22.87808888526706</v>
+        <v>22.87808890839352</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>1.031704685850572</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.1915744317372401</v>
+        <v>-0.1915744321265964</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5110,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>48.15529524225773</v>
+        <v>48.15529523425525</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>19.7107992943572</v>
+        <v>19.71079933393996</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>1.649037471566105</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.1667650627196914</v>
+        <v>-0.1667650628364989</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5163,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>37.1635754371842</v>
+        <v>37.16357542663297</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>16.87350913251257</v>
+        <v>16.87350930133317</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>0.6220159686264627</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.2109864397510212</v>
+        <v>-0.2109864397250648</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>40.77252138030745</v>
+        <v>40.77252145651015</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>21.96379934198058</v>
+        <v>21.96379936653261</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>0.4918371564372804</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0155764033596959</v>
+        <v>-0.01557640348948058</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>44.55140989863094</v>
+        <v>44.55140987825153</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>13.96089785711258</v>
+        <v>13.96089788036257</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-1.425587248421056</v>
+        <v>-1.425587248291268</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>237.8816705887379</v>
+        <v>237.881670588738</v>
       </c>
       <c r="E92" s="2" t="n">
         <v>127.5</v>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>34.91987974041824</v>
+        <v>34.9198795097312</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>12.97696194553589</v>
+        <v>12.97696206154622</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>0.8352331012409452</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.8782033300950001</v>
+        <v>-0.8782033290567237</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>234.2400448020725</v>
+        <v>234.2400448020724</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>89.2</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>35.12404507175991</v>
+        <v>35.12404480539568</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>17.93071925057663</v>
+        <v>17.93071944941106</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>0.9621708467024712</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.4948365691088927</v>
+        <v>-0.4948365706663271</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>39.68120852153761</v>
+        <v>39.68120863300165</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>13.54440823327485</v>
+        <v>13.54440825772829</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>0.8367183991488116</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.4773424464668279</v>
+        <v>-0.4773424468042709</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>42.40987571441958</v>
+        <v>42.40987572787235</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>18.66631841803529</v>
+        <v>18.66631845639528</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0.2388615937016738</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.6066177946077824</v>
+        <v>-0.6066177946856586</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>36.33721909298977</v>
+        <v>36.33721909884041</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>11.89911395834071</v>
+        <v>11.89911400838402</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.7088647421102982</v>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>41.04106358117504</v>
+        <v>41.04106353926579</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>14.54458384347341</v>
+        <v>14.5445837894609</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>0.5793334974259351</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-1.794214876103579</v>
+        <v>-1.794214876882355</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>220.8907140876711</v>
+        <v>220.8907140876718</v>
       </c>
       <c r="E98" s="2" t="n">
         <v>48.2</v>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>42.72261137385655</v>
+        <v>42.72261151552643</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>19.4402820444486</v>
+        <v>19.44028203172052</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.6455369966166463</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.2127286602613465</v>
+        <v>-0.2127286604690019</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>40.68829055885323</v>
+        <v>40.68829056401932</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>19.30406044905748</v>
+        <v>19.30406058612635</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.3277851763556027</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-2.662322785809681</v>
+        <v>-2.662322785978386</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>39.87430339923723</v>
+        <v>39.87430340127597</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>16.07269091723709</v>
+        <v>16.0726909347484</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>0.732448737896305</v>
@@ -5785,7 +5785,7 @@
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>213.992578252269</v>
+        <v>213.9925782522706</v>
       </c>
       <c r="E101" s="2" t="n">
         <v>35.45</v>
@@ -5799,10 +5799,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>36.64448632843487</v>
+        <v>36.64448647962521</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>16.00795412429219</v>
+        <v>16.00795407161245</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.5427307671178602</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.1323493480862767</v>
+        <v>-0.1323493481122316</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>41.74412485819607</v>
+        <v>41.7441248890414</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>16.10483769542439</v>
+        <v>16.10483790391011</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>0.4215792906941168</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.1021127027909715</v>
+        <v>-0.102112702959697</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>38.75829517534873</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>12.03675796292755</v>
+        <v>12.03675806765995</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.4552798044629044</v>
@@ -5944,7 +5944,7 @@
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>196.8052914312745</v>
+        <v>196.8052914312746</v>
       </c>
       <c r="E104" s="2" t="n">
         <v>61</v>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>40.18137479973824</v>
+        <v>40.18137515989376</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>21.9304835296479</v>
+        <v>21.93048348874958</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>1.02958028798918</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.05609541111465222</v>
+        <v>0.05609540916784084</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>171.8923795645469</v>
+        <v>171.8923795645468</v>
       </c>
       <c r="E105" s="2" t="n">
         <v>23.2</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>37.01438917751854</v>
+        <v>37.01438772758838</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>18.16633910633625</v>
+        <v>18.16634082012416</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>1.173065588498997</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.1595868411806254</v>
+        <v>-0.1595868389223357</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>171.738977737577</v>
+        <v>171.7389777375785</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>108</v>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>43.0796834240035</v>
+        <v>43.07968354876465</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>16.12535511014446</v>
+        <v>16.12535518403117</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>1.491893028793488</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.5333153709764629</v>
+        <v>-0.5333153720147675</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>47.70824979176303</v>
+        <v>47.70825010650694</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>11.32705224788188</v>
+        <v>11.32705217296843</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.7033086634740966</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.06779734638887819</v>
+        <v>0.06779734590866815</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>39.04530017218787</v>
+        <v>39.04530025725249</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>18.20537904403647</v>
+        <v>18.20537912989366</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.6093792743911375</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-25.85459688399067</v>
+        <v>-25.85459688476932</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>136.2855693354552</v>
+        <v>136.2855693354545</v>
       </c>
       <c r="E109" s="2" t="n">
         <v>32.25</v>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>38.0311444233766</v>
+        <v>38.03114515793416</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>18.87114521283742</v>
+        <v>18.87114529187345</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>0.2637962126132823</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.2893208648187467</v>
+        <v>-0.2893208650783236</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>39.42928373469721</v>
+        <v>39.4292838588584</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>21.49564502326353</v>
+        <v>21.49564508367213</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>1.235452198499643</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.2875912621471023</v>
+        <v>-0.2875912624975255</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>41.00225268692087</v>
+        <v>41.00225265806684</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>18.92605785373228</v>
+        <v>18.92605770829745</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.501698398289172</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-2.423439907959115</v>
+        <v>-2.423439907504846</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>116.1812168088303</v>
+        <v>116.1812168088304</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>45.7</v>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>31.76191439235775</v>
+        <v>31.76191441561846</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>11.60455401121164</v>
+        <v>11.60455407689306</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>1.186004476211294</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.2726743076077329</v>
+        <v>-0.2726743077764512</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>106.2281384094418</v>
+        <v>106.2281384094414</v>
       </c>
       <c r="E113" s="2" t="n">
         <v>18.5</v>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>49.17189697070339</v>
+        <v>49.17189695544685</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>6.53771727056706</v>
+        <v>6.537717299968499</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>0.762763858258577</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.02907943209277046</v>
+        <v>0.02907943214468557</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>57.88731979447381</v>
+        <v>57.88731979447366</v>
       </c>
       <c r="E114" s="2" t="n">
         <v>72.3</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>35.16830352376803</v>
+        <v>35.16830381854814</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>15.57303903348749</v>
+        <v>15.5730388209383</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>1.155096072214059</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.06504822902631313</v>
+        <v>0.06504822850717429</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>40.45289783597476</v>
+        <v>40.45289783597504</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>56.5</v>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>22.82307696936611</v>
+        <v>22.82307701330924</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>16.14584122399383</v>
+        <v>16.14584114068564</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.6973022282200585</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.2827038228541241</v>
+        <v>-0.2827038231396533</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>21.31005534658614</v>
+        <v>21.31005534658615</v>
       </c>
       <c r="E116" s="2" t="n">
         <v>17.95</v>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>48.5124896867868</v>
+        <v>48.51248972795864</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>9.310229972946777</v>
+        <v>9.310229865554501</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.1556555978811549</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.08810602397990547</v>
+        <v>0.0881060235645888</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>

--- a/output/full_scan/batch_seq6_2026-10-22.xlsx
+++ b/output/full_scan/batch_seq6_2026-10-22.xlsx
@@ -444,7 +444,7 @@
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>78.90131156175438</v>
+        <v>78.901311650401</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>33.15849061754602</v>
+        <v>33.15849069222572</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.887832827195892</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1917634640524146</v>
+        <v>0.191763463912249</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>88.80743663051797</v>
+        <v>88.80743663339511</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>40.42124236999416</v>
+        <v>40.42124235158894</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>4.685271930498494</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>67.03613243533684</v>
+        <v>67.03613181539461</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>19.45238169571356</v>
+        <v>19.45238179633244</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>2.026592574560778</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.04737782209310933</v>
+        <v>0.04737782212114357</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>65.6407222068942</v>
+        <v>65.64072225781808</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>34.89015513951923</v>
+        <v>34.8901552567762</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>2.416036974209795</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.3201726229496833</v>
+        <v>-0.3201726228095172</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>55.0856830495019</v>
+        <v>55.08568306302619</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>36.65148684351382</v>
+        <v>36.65148697570977</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>1.233027650764054</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-5.186169113878286</v>
+        <v>-5.186169114262666</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>857.2373126052629</v>
+        <v>857.2373126052628</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>90.09999999999999</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>60.41895069619824</v>
+        <v>60.41895152803244</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>33.02733246566626</v>
+        <v>33.02733296206482</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1.281559472437751</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.02741526840408426</v>
+        <v>0.02741526644170511</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>54.64295263835304</v>
+        <v>54.64295267003019</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>33.47085421456798</v>
+        <v>33.47085420987621</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>0.6145525805647692</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.6052151005438731</v>
+        <v>-0.6052151007120763</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>66.14815023444106</v>
+        <v>66.14815027975249</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>33.13629602100019</v>
+        <v>33.13629602271578</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>2.544511166061138</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.7480122021666666</v>
+        <v>0.7480122020405191</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>60.06618490310662</v>
+        <v>60.06618492723181</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>49.94953734204721</v>
+        <v>49.94953748794686</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>1.398229788631511</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1.547504950749008</v>
+        <v>1.547504950678921</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>59.64192344313563</v>
+        <v>59.64192350656069</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>26.41004659100323</v>
+        <v>26.41004665243693</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>3.166044129630837</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>2.003902512580358</v>
+        <v>2.00390251196362</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>712.1949567710933</v>
+        <v>712.1949567710934</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>26.85</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>82.00485241673489</v>
+        <v>82.00485252903977</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>52.30388558433571</v>
+        <v>52.30388560759321</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>2.033008627467827</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.2300014569881352</v>
+        <v>0.2300014569320661</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>49.94045106699661</v>
+        <v>49.94045126700379</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>36.37853757561509</v>
+        <v>36.37853763934768</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>0.6998040680600051</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.9585343487223748</v>
+        <v>-0.9585343506847472</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>677.0219967973212</v>
+        <v>677.0219967973214</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>45.9</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>68.14931598112399</v>
+        <v>68.14931621063776</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>35.44148194933189</v>
+        <v>35.44148200241577</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>0.6476559223050367</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.2317171873639329</v>
+        <v>0.2317171871396633</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>673.8203676915855</v>
+        <v>673.8203676915966</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>32.6</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>69.44974491603531</v>
+        <v>69.4497452865578</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>41.35617015557782</v>
+        <v>41.35617013089941</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>5.971524141804417</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.07751029840802381</v>
+        <v>0.07751029816973354</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>64.81172467745395</v>
+        <v>64.81172469291985</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>51.3059022253042</v>
+        <v>51.30590226155739</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>1.252859594182261</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>3.795119547750986</v>
+        <v>3.79511954747063</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>640.8772581040774</v>
+        <v>640.8772581040773</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>89.8</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>53.90440152316441</v>
+        <v>53.90440182572696</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>28.80512429673319</v>
+        <v>28.80512431046055</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>0.6183082921517314</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.1028913194221461</v>
+        <v>0.1028913205434878</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>42.48192271990463</v>
+        <v>42.4819225802676</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>30.04794246560368</v>
+        <v>30.0479422159358</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0.2501599396096814</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-1.291802676415414</v>
+        <v>-1.291802675966877</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>619.4782183600238</v>
+        <v>619.478218360023</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>472</v>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>55.82687234176015</v>
+        <v>55.82687230544324</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>22.08385990619946</v>
+        <v>22.08385989167767</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>1.865041219778342</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>4.108932051413049</v>
+        <v>4.108932053235302</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>610.6013962923113</v>
+        <v>610.6013962923114</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>50</v>
@@ -1509,7 +1509,7 @@
         <v>61.76466998866634</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>25.21165818000409</v>
+        <v>25.21165813999458</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>1.140741378769861</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>50.40165487128143</v>
+        <v>50.40165490756138</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>26.14804729550728</v>
+        <v>26.14804748521312</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>0.5791253972083167</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-1.693799944578823</v>
+        <v>-1.693799945167536</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>50.72621446759339</v>
+        <v>50.72621449826526</v>
       </c>
       <c r="I22" s="2" t="n">
         <v>31.53902381118123</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-8.311415718366369</v>
+        <v>-8.311415719347643</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>52.29308520366342</v>
+        <v>52.29308520662966</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>7.385866887955562</v>
+        <v>7.38586689999112</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>0.9435408730111927</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.368099772991384</v>
+        <v>0.3680997728792484</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>42.43749229197072</v>
+        <v>42.43749232377858</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>28.93118721219972</v>
+        <v>28.9311873203415</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>0.5603887573874565</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-5.813970494418005</v>
+        <v>-5.813970494558173</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>60.52530552710639</v>
+        <v>60.5253055440927</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>31.63464738002723</v>
+        <v>31.63464752250954</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>2.53425075941183</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-5.099216838482505</v>
+        <v>-5.099216839463779</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>66.95384635554649</v>
+        <v>66.95384638707176</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>36.24106969201431</v>
+        <v>36.24106969418396</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>13.57004154429711</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1.280897501444539</v>
+        <v>1.280897502159402</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>558.1509004929636</v>
+        <v>558.1509004929643</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>115</v>
@@ -1880,7 +1880,7 @@
         <v>58.25200599885891</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>23.86490113444244</v>
+        <v>23.86490113878756</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>1.29480849990638</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.4687413739361129</v>
+        <v>0.4687413742164473</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>43.48960113609603</v>
+        <v>43.48960112933737</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>21.20336236407856</v>
+        <v>21.2033623532975</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>2.152664272709147</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.415568662340154</v>
+        <v>0.4155686624122242</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>43.96007258936589</v>
+        <v>43.96007259541209</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>36.0598886415957</v>
+        <v>36.05988865340181</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>0.5113305909110898</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-1.205038108072437</v>
+        <v>-1.205038108100469</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>45.18736474461694</v>
+        <v>45.18736474405657</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>22.21152693855917</v>
+        <v>22.21152701898373</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>0.7864727676954077</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-6.192578775255869</v>
+        <v>-6.192578775536179</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>43.41363655403386</v>
+        <v>43.41363661848646</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>20.82925010494149</v>
+        <v>20.82925006630665</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>0.1866793272497344</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.7767470555385939</v>
+        <v>-0.7767470557488475</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>493.2204727641995</v>
+        <v>493.2204727641996</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>104.5</v>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>50.04581625924752</v>
+        <v>50.04581616094982</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>24.01983942891731</v>
+        <v>24.01983941284163</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>0.4830325583215399</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-1.378983244925559</v>
+        <v>-1.378983244028463</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>56.53966589134033</v>
+        <v>56.53966588171265</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>31.24587078004762</v>
+        <v>31.24587079558084</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0.3407759209715591</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.1250449840208798</v>
+        <v>0.1250449841470225</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>57.32572722921451</v>
+        <v>57.32572725445404</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>40.65618557774729</v>
+        <v>40.65618564660782</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0.8579285059578369</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.1599100455332787</v>
+        <v>0.159910045505243</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>43.43573050919412</v>
+        <v>43.43573047366545</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>10.92814117291418</v>
+        <v>10.92814104955457</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>0.6308991060770219</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>3.220756256180326</v>
+        <v>3.220756260805814</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>41.01842365791195</v>
+        <v>41.01842369221229</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>22.25653663076563</v>
+        <v>22.25653665270901</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>0.7881131899594851</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-3.016949128362338</v>
+        <v>-3.016949128502516</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>45.64879488325099</v>
+        <v>45.64879489604579</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>26.36145686716847</v>
+        <v>26.36145702610619</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>0.6606877362996376</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.5764223443898869</v>
+        <v>-0.5764223444879946</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>44.38903008640304</v>
+        <v>44.38903009914875</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>24.47871251068761</v>
+        <v>24.47871255214793</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>0.4188212073909783</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-1.497159607495197</v>
+        <v>-1.497159607565285</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>51.9979942215828</v>
+        <v>51.99799423528582</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>28.03045122781381</v>
+        <v>28.03045121788873</v>
       </c>
       <c r="J39" s="2" t="n">
         <v>0.8073056122401421</v>
@@ -2531,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.3724378742135421</v>
+        <v>-0.3724378743537136</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>451.6897327308895</v>
+        <v>451.6897327308894</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>317</v>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>43.03512732561887</v>
+        <v>43.03512732954065</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>22.96535419368785</v>
+        <v>22.96535423670838</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>0.743549978550329</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-5.526473732019731</v>
+        <v>-5.526473731459085</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>448.789026031717</v>
+        <v>448.7890260317168</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>18.85</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>54.17252476598073</v>
+        <v>54.1725247833237</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>6.465255837183021</v>
+        <v>6.465255830240836</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>0.4978017104403912</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.003570395574027052</v>
+        <v>-0.003570395616077082</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>30.97607562471484</v>
+        <v>30.97607563505603</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>29.1060332513963</v>
+        <v>29.10603323831181</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>0.4070879222902932</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-11.864433325469</v>
+        <v>-11.8644333215443</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>443.2818300350431</v>
+        <v>443.2818300350429</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>910</v>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.47606460457181</v>
+        <v>51.47606490853165</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>15.70882899671447</v>
+        <v>15.7088290677179</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>0.7153998161566312</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>6.120000208557011</v>
+        <v>6.120000202389516</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>43.07001024196642</v>
+        <v>43.07001028968867</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>20.31186077810607</v>
+        <v>20.31186084108358</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>0.7271413870251814</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.6595038251268825</v>
+        <v>-0.6595038252810588</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>425.7006018832119</v>
+        <v>425.700601883212</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>96.3</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>43.07267998026353</v>
+        <v>43.07268021240122</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>16.10236348642621</v>
+        <v>16.10236351986086</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>0.8213115440132339</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.6177699451139422</v>
+        <v>-0.6177699456746359</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>425.3396473012075</v>
+        <v>425.3396473012078</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>103.5</v>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>29.04880106999937</v>
+        <v>29.04880107972087</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>24.0047379485804</v>
+        <v>24.00473798756883</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.4395881901848726</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-2.287462812416705</v>
+        <v>-2.287462812697045</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>422.4097094944597</v>
+        <v>422.4097094944589</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>21.2</v>
@@ -2940,7 +2940,7 @@
         <v>39.33646449845289</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>15.17390352224302</v>
+        <v>15.17390364062785</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.7280176980431818</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.1138734203328983</v>
+        <v>-0.1138734203749517</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>48.26300868512116</v>
+        <v>48.26300871833809</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>31.65186784950163</v>
+        <v>31.65186787716851</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>1.577254236615266</v>
@@ -3043,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>40.20477836627167</v>
+        <v>40.20477840928482</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>25.52246566965961</v>
+        <v>25.52246586417724</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>0.4165843898479347</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-2.115153758404115</v>
+        <v>-2.115153759357254</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>43.62316828151636</v>
+        <v>43.62316830666394</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>21.68590023469326</v>
+        <v>21.68590035780623</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>0.5971790049014803</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-1.982313017273315</v>
+        <v>-1.982313017974166</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>390.3716792665695</v>
+        <v>390.3716792665684</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>66.40000000000001</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>36.5163003784789</v>
+        <v>36.51630040431031</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>17.05801356902393</v>
+        <v>17.05801364001351</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>0.6658116057695529</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.7485696732402938</v>
+        <v>-0.7485696733243925</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>387.7442054053459</v>
+        <v>387.7442054053425</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>64.7</v>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>35.69826600268608</v>
+        <v>35.69826603385852</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>22.20425659630393</v>
+        <v>22.20425660015665</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>0.6613033381130128</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-1.095400227653411</v>
+        <v>-1.095400228045884</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3255,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>49.63021895151141</v>
+        <v>49.63021908967129</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>13.52333661687568</v>
+        <v>13.52333669288898</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>0.5770372728174034</v>
@@ -3273,7 +3273,7 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.1053667728702124</v>
+        <v>0.1053667724216608</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>42.46093502926755</v>
+        <v>42.46093504137975</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>22.68086874762121</v>
+        <v>22.68086876616175</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>1.209624947391127</v>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>48.88100525967484</v>
+        <v>48.88100534147562</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>11.42720954479049</v>
+        <v>11.42720962895418</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>0.8040499993026722</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.1525767165778569</v>
+        <v>-0.1525767168021311</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>48.71126886024458</v>
+        <v>48.71126890971599</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>19.71376691315064</v>
+        <v>19.7137669221596</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>0.5190079314417678</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.02471207143220994</v>
+        <v>0.0247120714041755</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>362.1305553446717</v>
+        <v>362.1305553446718</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>49.3</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>46.96597950069045</v>
+        <v>46.96597950348534</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>17.75779143753459</v>
+        <v>17.75779144220804</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>0.504251063292833</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.9111276447319314</v>
+        <v>-0.9111276447599703</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>359.8901219766542</v>
+        <v>359.8901219766538</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>1260</v>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>41.9803274788225</v>
+        <v>41.98032749528994</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>23.61668679874655</v>
+        <v>23.61668686191035</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>0.6588398461457313</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-28.88229394266896</v>
+        <v>-28.88229394519234</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>358.1073475243697</v>
+        <v>358.1073475243678</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>40.5</v>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>42.3496372319269</v>
+        <v>42.3496372579198</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>20.04113881620643</v>
+        <v>20.04113881941166</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>0.7065556234253727</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.3333043153864979</v>
+        <v>-0.333304315484624</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>45.09504446452429</v>
+        <v>45.09504468261159</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>23.82667916190858</v>
+        <v>23.82667923723947</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>1.176351588861237</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-6.293124571423642</v>
+        <v>-6.293124568760396</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>352.6703790402014</v>
+        <v>352.6703790402013</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>39.75</v>
@@ -3682,7 +3682,7 @@
         <v>39.2925975933078</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>18.12821706449261</v>
+        <v>18.12821702997862</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>0.9505886200777706</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.01006520370288294</v>
+        <v>0.01006520367485725</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3732,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>42.67162790447533</v>
+        <v>42.67162789016278</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>15.80925978272022</v>
+        <v>15.80925958917357</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>0.720218977300666</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-1.450102454787583</v>
+        <v>-1.45010245477356</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>44.06658278474664</v>
+        <v>44.06658274309965</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>23.80406055080532</v>
+        <v>23.80406054722563</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>0.3986958506219546</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.0188120780633162</v>
+        <v>0.01881207809134067</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>342.5937962191654</v>
+        <v>342.5937962191653</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>21.45</v>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>41.08666673932102</v>
+        <v>41.08666680288282</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>12.0018683298396</v>
+        <v>12.00186851463728</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>0.3186330594557458</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.1947943164356323</v>
+        <v>-0.194794316617853</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>338.7687621748493</v>
+        <v>338.7687621748494</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>54.3</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>40.60047027464629</v>
+        <v>40.60047036519811</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>12.96595018636582</v>
+        <v>12.9659502304512</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>0.4458939642293094</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.4713973303740281</v>
+        <v>-0.4713973304721505</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>36.48514494369422</v>
+        <v>36.48514492911995</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>20.51815889733559</v>
+        <v>20.51815898728553</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>0.7673668027537495</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-4.996363064771156</v>
+        <v>-4.99636306463097</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>40.93190921581994</v>
+        <v>40.93190904364949</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>9.750587199300613</v>
+        <v>9.750586983917623</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>0.4426821867782229</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.02268243914230822</v>
+        <v>-0.02268243891803745</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4050,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>42.30688816675527</v>
+        <v>42.30688822339985</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15.29926213219526</v>
+        <v>15.29926216213074</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>0.6291091592888773</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.1351173207320366</v>
+        <v>-0.1351173208161472</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>43.57309476926993</v>
+        <v>43.57309488806039</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>15.28813054035275</v>
+        <v>15.28813049515237</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>0.3142562496879532</v>
@@ -4121,7 +4121,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.8109780195459975</v>
+        <v>-0.8109780199104366</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4156,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>32.03038264205276</v>
+        <v>32.03038265836361</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>24.49085424502265</v>
+        <v>24.4908542707221</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.58591246754207</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.2211326876452091</v>
+        <v>-0.221132687673246</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>60.85382488330799</v>
+        <v>60.85382493329802</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>19.37674930391606</v>
+        <v>19.37674946537529</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>0.8343576285214932</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>37.92822110967214</v>
+        <v>37.92822120389889</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>22.45138767198857</v>
+        <v>22.45138783321344</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>0.8133622177079534</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-5.147699666147743</v>
+        <v>-5.147699666007562</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>43.7557326243288</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>14.87684339446275</v>
+        <v>14.87684335649412</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>0.6373885306045443</v>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>42.54610963574236</v>
+        <v>42.54610978979809</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>14.49868891398552</v>
+        <v>14.49868898414089</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>0.7337116262418329</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.06644144042400554</v>
+        <v>-0.06644144050810967</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>34.96580267047571</v>
+        <v>34.96580266501265</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>20.09652617979782</v>
+        <v>20.09652616254519</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>0.934941983401482</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-5.815837257575128</v>
+        <v>-5.815837257434911</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>46.23577657025787</v>
+        <v>46.23577715539861</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>9.103864503199361</v>
+        <v>9.103864649271475</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>1.560135065854949</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.1214513132016611</v>
+        <v>-0.121451313682109</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>52.22630981911153</v>
+        <v>52.22630985095005</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>13.04338897257761</v>
+        <v>13.04338885363556</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>0.4506725487651918</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.444089150789291</v>
+        <v>-0.4440891515321899</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>311.9804891749366</v>
+        <v>311.980489174938</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>50.5</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>38.12016304578459</v>
+        <v>38.12016311522286</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>6.852570144367955</v>
+        <v>6.852569993156149</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>2.427258755264709</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.02594204660493094</v>
+        <v>-0.02594204666099717</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>308.8541683362196</v>
+        <v>308.8541683362195</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>74.09999999999999</v>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>37.21330444108085</v>
+        <v>37.21330496129914</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>9.465805422527808</v>
+        <v>9.465805455445979</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>0.9879476334987756</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.2680275236563803</v>
+        <v>-0.2680275238526175</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>48.09318561686796</v>
+        <v>48.09318560519053</v>
       </c>
       <c r="I80" s="2" t="n">
         <v>15.26455533280837</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.06866616052791649</v>
+        <v>-0.06866616047183249</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>42.26263508135629</v>
+        <v>42.26263505807903</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>13.48209430188449</v>
+        <v>13.48209429719711</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>0.5314520845681304</v>
@@ -4778,7 +4778,7 @@
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>282.251971329263</v>
+        <v>282.2519713292633</v>
       </c>
       <c r="E82" s="2" t="n">
         <v>97.3</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>33.0066884658544</v>
+        <v>33.00668855393134</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>27.51638200017733</v>
+        <v>27.51638209591686</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>1.513697526763331</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.4252203472449203</v>
+        <v>-0.4252203476654333</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>39.636476738601</v>
+        <v>39.63647675281566</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>29.14200504635948</v>
+        <v>29.14200513778649</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>0.7055078030690214</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-1.92155247161646</v>
+        <v>-1.921552468532762</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>275.8955318291405</v>
+        <v>275.8955318291406</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>213</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>32.17204049819425</v>
+        <v>32.17204053151654</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>18.61855957768476</v>
+        <v>18.61855965765578</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>0.4418196652627401</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-4.277029717507125</v>
+        <v>-4.277029717675313</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>39.7425334334281</v>
+        <v>39.7425334415413</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>19.82601724467363</v>
+        <v>19.82601734464073</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>1.730924899218151</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-30.57943230678627</v>
+        <v>-30.57943231071072</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>38.50361059945103</v>
+        <v>38.50361063387068</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>16.77364683899512</v>
+        <v>16.77364686166716</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>0.6177546508757084</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.3803953205665522</v>
+        <v>-0.380395320818852</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>38.74714832246571</v>
+        <v>38.74714783330152</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>22.87808890839352</v>
+        <v>22.8780889848114</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>1.031704685850572</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.1915744321265964</v>
+        <v>-0.1915744322667622</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>257.774819400156</v>
+        <v>257.7748194001568</v>
       </c>
       <c r="E88" s="2" t="n">
         <v>26</v>
@@ -5110,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>48.15529523425525</v>
+        <v>48.15529530021113</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>19.71079933393996</v>
+        <v>19.71079938292834</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>1.649037471566105</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.1667650628364989</v>
+        <v>-0.1667650629906861</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>256.7303568862035</v>
+        <v>256.7303568862033</v>
       </c>
       <c r="E89" s="2" t="n">
         <v>27.9</v>
@@ -5163,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>37.16357542663297</v>
+        <v>37.16357538838862</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>16.87350930133317</v>
+        <v>16.87350925920635</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>0.6220159686264627</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.2109864397250648</v>
+        <v>-0.2109864397110513</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>40.77252145651015</v>
+        <v>40.77252154277039</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>21.96379936653261</v>
+        <v>21.96379932562726</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>0.4918371564372804</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.01557640348948058</v>
+        <v>-0.01557640353153306</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>44.55140987825153</v>
+        <v>44.55140991743646</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>13.96089788036257</v>
+        <v>13.96089770128274</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-1.425587248291268</v>
+        <v>-1.425587248627676</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>237.881670588738</v>
+        <v>237.8816705887381</v>
       </c>
       <c r="E92" s="2" t="n">
         <v>127.5</v>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>34.9198795097312</v>
+        <v>34.91987954716525</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>12.97696206154622</v>
+        <v>12.97696210844495</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>0.8352331012409452</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.8782033290567237</v>
+        <v>-0.8782033297575751</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>234.2400448020724</v>
+        <v>234.2400448020728</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>89.2</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>35.12404480539568</v>
+        <v>35.12404516396292</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>17.93071944941106</v>
+        <v>17.93071957472839</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>0.9621708467024712</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.4948365706663271</v>
+        <v>-0.4948365745910894</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>232.5910084003217</v>
+        <v>232.5910084003216</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>72.5</v>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>39.68120863300165</v>
+        <v>39.68120857977471</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>13.54440825772829</v>
+        <v>13.54440836878628</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>0.8367183991488116</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.4773424468042709</v>
+        <v>-0.4773424464117937</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>42.40987572787235</v>
+        <v>42.40987573464388</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>18.66631845639528</v>
+        <v>18.66631862181538</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0.2388615937016738</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.6066177946856586</v>
+        <v>-0.6066177946576288</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>36.33721909884041</v>
+        <v>36.33721911774246</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>11.89911400838402</v>
+        <v>11.89911408489632</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.7088647421102982</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.6654665395920856</v>
+        <v>-0.6654665395640569</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>41.04106353926579</v>
+        <v>41.04106365038107</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>14.5445837894609</v>
+        <v>14.54458377371955</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>0.5793334974259351</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-1.794214876882355</v>
+        <v>-1.794214879125021</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>220.8907140876718</v>
+        <v>220.8907140876705</v>
       </c>
       <c r="E98" s="2" t="n">
         <v>48.2</v>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>42.72261151552643</v>
+        <v>42.7226114936282</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>19.44028203172052</v>
+        <v>19.44028202468623</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.6455369966166463</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.2127286604690019</v>
+        <v>-0.2127286604409696</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>40.68829056401932</v>
+        <v>40.68829057730525</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>19.30406058612635</v>
+        <v>19.30406054645067</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.3277851763556027</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-2.662322785978386</v>
+        <v>-2.662322786034475</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>215.1517507111491</v>
+        <v>215.1517507111496</v>
       </c>
       <c r="E100" s="2" t="n">
         <v>4890</v>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>39.87430340127597</v>
+        <v>39.87430339762433</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>16.0726909347484</v>
+        <v>16.07269091214538</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>0.732448737896305</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-75.60938772808734</v>
+        <v>-75.60938772668523</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>213.9925782522706</v>
+        <v>213.9925782522711</v>
       </c>
       <c r="E101" s="2" t="n">
         <v>35.45</v>
@@ -5799,10 +5799,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>36.64448647962521</v>
+        <v>36.64448615213342</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>16.00795407161245</v>
+        <v>16.00795425620245</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.5427307671178602</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.1323493481122316</v>
+        <v>-0.1323493478879627</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>41.7441248890414</v>
+        <v>41.74412493609269</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>16.10483790391011</v>
+        <v>16.10483794033801</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>0.4215792906941168</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.102112702959697</v>
+        <v>-0.102112703001747</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>38.75829517534873</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>12.03675806765995</v>
+        <v>12.0367580421686</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.4552798044629044</v>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>40.18137515989376</v>
+        <v>40.18137544932964</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>21.93048348874958</v>
+        <v>21.93048346021575</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>1.02958028798918</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.05609540916784084</v>
+        <v>0.05609540874734253</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>171.8923795645468</v>
+        <v>171.8923795645469</v>
       </c>
       <c r="E105" s="2" t="n">
         <v>23.2</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>37.01438772758838</v>
+        <v>37.01438775780172</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>18.16634082012416</v>
+        <v>18.16634120023194</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>1.173065588498997</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.1595868389223357</v>
+        <v>-0.1595868391185751</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>43.07968354876465</v>
+        <v>43.07968339761172</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>16.12535518403117</v>
+        <v>16.12535523466551</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>1.491893028793488</v>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>47.70825010650694</v>
+        <v>47.70825042663109</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>11.32705217296843</v>
+        <v>11.32705202112528</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.7033086634740966</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.06779734590866815</v>
+        <v>0.06779734564234507</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>151.7663236061505</v>
+        <v>151.7663236061507</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>1410</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>39.04530025725249</v>
+        <v>39.04530018387027</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>18.20537912989366</v>
+        <v>18.20537911898719</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.6093792743911375</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-25.85459688476932</v>
+        <v>-25.85459686850967</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>136.2855693354545</v>
+        <v>136.2855693354553</v>
       </c>
       <c r="E109" s="2" t="n">
         <v>32.25</v>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>38.03114515793416</v>
+        <v>38.03114442274243</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>18.87114529187345</v>
+        <v>18.87114541205426</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>0.2637962126132823</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.2893208650783236</v>
+        <v>-0.2893208637887592</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>39.4292838588584</v>
+        <v>39.42928396553069</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>21.49564508367213</v>
+        <v>21.49564517636999</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>1.235452198499643</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.2875912624975255</v>
+        <v>-0.2875912625816328</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>41.00225265806684</v>
+        <v>41.00225269182219</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>18.92605770829745</v>
+        <v>18.92605770781575</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.501698398289172</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-2.423439907504846</v>
+        <v>-2.423439907967414</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>31.76191441561846</v>
+        <v>31.76191442993274</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>11.60455407689306</v>
+        <v>11.60455413410972</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>1.186004476211294</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.2726743077764512</v>
+        <v>-0.2726743078605591</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>106.2281384094414</v>
+        <v>106.2281384094417</v>
       </c>
       <c r="E113" s="2" t="n">
         <v>18.5</v>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>49.17189695544685</v>
+        <v>49.17189696005254</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>6.537717299968499</v>
+        <v>6.537717339499033</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>0.762763858258577</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.02907943214468557</v>
+        <v>0.02907943210263628</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>57.88731979447366</v>
+        <v>57.88731979447398</v>
       </c>
       <c r="E114" s="2" t="n">
         <v>72.3</v>
@@ -6488,7 +6488,7 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>35.16830381854814</v>
+        <v>35.16830362498676</v>
       </c>
       <c r="I114" s="2" t="n">
         <v>15.5730388209383</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.06504822850717429</v>
+        <v>0.06504822878750138</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>40.45289783597504</v>
+        <v>40.45289783597484</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>56.5</v>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>22.82307701330924</v>
+        <v>22.82307732613796</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>16.14584114068564</v>
+        <v>16.14584101148633</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.6973022282200585</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.2827038231396533</v>
+        <v>-0.282703823307857</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>21.31005534658615</v>
+        <v>21.31005534658614</v>
       </c>
       <c r="E116" s="2" t="n">
         <v>17.95</v>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>48.51248972795864</v>
+        <v>48.51248975829579</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>9.310229865554501</v>
+        <v>9.310229858511908</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.1556555978811549</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0881060235645888</v>
+        <v>0.08810602338236645</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
